--- a/Deliverables/Fase2 Sprint1/v4-ASVS-checklist-en.xlsx
+++ b/Deliverables/Fase2 Sprint1/v4-ASVS-checklist-en.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diana\Documents\github\desofs2025_wed_ffs_3\Deliverables\Fase2 Sprint1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myisepipp-my.sharepoint.com/personal/1211149_isep_ipp_pt/Documents/Documents/GitHub/desofs2025_wed_ffs_3/Deliverables/Fase2 Sprint1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EEE81CE-41DC-44A0-B883-E7354B326F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{9EEE81CE-41DC-44A0-B883-E7354B326F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60B1C785-D19F-4FDA-8BA7-0E5DCD30BE5F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="885" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="885" firstSheet="2" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASVS Results" sheetId="1" r:id="rId1"/>
@@ -5961,18 +5961,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -5995,6 +5983,18 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6084,7 +6084,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-PT"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -6258,7 +6258,7 @@
                   <c:v>84.615384615384613</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>94.642857142857139</c:v>
+                  <c:v>55.357142857142861</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>65</c:v>
@@ -6297,7 +6297,7 @@
                   <c:v>41.666666666666671</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>62.45353159851301</c:v>
+                  <c:v>54.27509293680297</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6513,12 +6513,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -6815,18 +6811,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AMJ16"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="64.26953125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="23.26953125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="64.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="4" customWidth="1"/>
     <col min="3" max="3" width="21" style="4" customWidth="1"/>
     <col min="4" max="4" width="25" style="4" customWidth="1"/>
     <col min="5" max="5" width="37" style="4" customWidth="1"/>
-    <col min="6" max="6" width="11.08984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="1024" width="8.81640625" style="4"/>
+    <col min="6" max="6" width="11.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="1024" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="42" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -6843,7 +6839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
@@ -6860,17 +6856,17 @@
         <v>84.615384615384613</v>
       </c>
       <c r="E2" s="12"/>
-      <c r="F2" s="174" t="s">
+      <c r="F2" s="170" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="9">
         <f>COUNTIF(Authentication!G2:G58,"Valid")</f>
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C3" s="10">
         <f>COUNTIF(Authentication!G2:G58,"&lt;&gt;Not Applicable")</f>
@@ -6878,14 +6874,14 @@
       </c>
       <c r="D3" s="11">
         <f t="shared" si="0"/>
-        <v>94.642857142857139</v>
+        <v>55.357142857142861</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="174" t="s">
+      <c r="F3" s="170" t="s">
         <v>1237</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -6902,11 +6898,11 @@
         <v>65</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="174" t="s">
+      <c r="F4" s="170" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>10</v>
       </c>
@@ -6923,11 +6919,11 @@
         <v>77.777777777777786</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="174" t="s">
+      <c r="F5" s="170" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>11</v>
       </c>
@@ -6948,7 +6944,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
@@ -6965,11 +6961,11 @@
         <v>50</v>
       </c>
       <c r="E7" s="12"/>
-      <c r="F7" s="174" t="s">
+      <c r="F7" s="170" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
@@ -6990,7 +6986,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>15</v>
       </c>
@@ -7011,7 +7007,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>16</v>
       </c>
@@ -7032,7 +7028,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>17</v>
       </c>
@@ -7053,7 +7049,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>19</v>
       </c>
@@ -7074,7 +7070,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>20</v>
       </c>
@@ -7095,7 +7091,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>21</v>
       </c>
@@ -7116,7 +7112,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>22</v>
       </c>
@@ -7137,13 +7133,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="9">
         <f>SUM(B2:B15)</f>
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="C16" s="10">
         <f>SUM(C2:C15)</f>
@@ -7151,7 +7147,7 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="0"/>
-        <v>62.45353159851301</v>
+        <v>54.27509293680297</v>
       </c>
       <c r="E16" s="12"/>
     </row>
@@ -7169,20 +7165,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AMJ18"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.7265625" style="64" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" style="20"/>
-    <col min="3" max="5" width="8.81640625" style="52"/>
+    <col min="1" max="1" width="30.7109375" style="64" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="20"/>
+    <col min="3" max="5" width="8.85546875" style="52"/>
     <col min="6" max="6" width="93" style="20" customWidth="1"/>
-    <col min="7" max="7" width="12.453125" style="20" customWidth="1"/>
-    <col min="8" max="8" width="35.81640625" style="20" customWidth="1"/>
-    <col min="9" max="9" width="17.453125" style="20" customWidth="1"/>
-    <col min="10" max="10" width="30.81640625" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="7" max="7" width="12.42578125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="35.85546875" style="20" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" style="20" customWidth="1"/>
+    <col min="10" max="10" width="30.85546875" style="20" customWidth="1"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="36" customFormat="1" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="36" customFormat="1" ht="42.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="95" t="s">
         <v>24</v>
       </c>
@@ -7214,8 +7210,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="164" t="s">
+    <row r="2" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="175" t="s">
         <v>592</v>
       </c>
       <c r="B2" s="98" t="s">
@@ -7242,8 +7238,8 @@
         <v>596</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="164"/>
+    <row r="3" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="175"/>
       <c r="B3" s="98" t="s">
         <v>597</v>
       </c>
@@ -7268,8 +7264,8 @@
         <v>600</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="164"/>
+    <row r="4" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="175"/>
       <c r="B4" s="98" t="s">
         <v>601</v>
       </c>
@@ -7296,8 +7292,8 @@
         <v>605</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="388" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="164"/>
+    <row r="5" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175"/>
       <c r="B5" s="98" t="s">
         <v>606</v>
       </c>
@@ -7322,8 +7318,8 @@
         <v>609</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="388" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="164"/>
+    <row r="6" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="175"/>
       <c r="B6" s="98" t="s">
         <v>610</v>
       </c>
@@ -7348,8 +7344,8 @@
         <v>613</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="326" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="164"/>
+    <row r="7" spans="1:10" ht="331.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="175"/>
       <c r="B7" s="98" t="s">
         <v>614</v>
       </c>
@@ -7374,8 +7370,8 @@
         <v>617</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="388" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="164" t="s">
+    <row r="8" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="175" t="s">
         <v>618</v>
       </c>
       <c r="B8" s="98" t="s">
@@ -7402,8 +7398,8 @@
         <v>622</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="357" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="164"/>
+    <row r="9" spans="1:10" ht="378.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="175"/>
       <c r="B9" s="98" t="s">
         <v>623</v>
       </c>
@@ -7430,8 +7426,8 @@
         <v>627</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="388" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="164"/>
+    <row r="10" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="175"/>
       <c r="B10" s="98" t="s">
         <v>628</v>
       </c>
@@ -7456,8 +7452,8 @@
         <v>631</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="357" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="164" t="s">
+    <row r="11" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="175" t="s">
         <v>632</v>
       </c>
       <c r="B11" s="98" t="s">
@@ -7486,8 +7482,8 @@
         <v>637</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="295" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="164"/>
+    <row r="12" spans="1:10" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="175"/>
       <c r="B12" s="98" t="s">
         <v>638</v>
       </c>
@@ -7512,8 +7508,8 @@
         <v>641</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="310.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="164"/>
+    <row r="13" spans="1:10" ht="347.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="175"/>
       <c r="B13" s="98" t="s">
         <v>642</v>
       </c>
@@ -7538,8 +7534,8 @@
         <v>645</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="326" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="164"/>
+    <row r="14" spans="1:10" ht="394.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="175"/>
       <c r="B14" s="98" t="s">
         <v>646</v>
       </c>
@@ -7564,8 +7560,8 @@
         <v>649</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="357" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="164"/>
+    <row r="15" spans="1:10" ht="363" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="175"/>
       <c r="B15" s="98" t="s">
         <v>650</v>
       </c>
@@ -7590,8 +7586,8 @@
         <v>653</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="326" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="164"/>
+    <row r="16" spans="1:10" ht="331.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="175"/>
       <c r="B16" s="98" t="s">
         <v>654</v>
       </c>
@@ -7616,8 +7612,8 @@
         <v>657</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="372.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="164"/>
+    <row r="17" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="175"/>
       <c r="B17" s="98" t="s">
         <v>658</v>
       </c>
@@ -7642,8 +7638,8 @@
         <v>661</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="403.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="164"/>
+    <row r="18" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="175"/>
       <c r="B18" s="98" t="s">
         <v>662</v>
       </c>
@@ -7692,20 +7688,20 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:AMJ26"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.81640625" style="64" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="20" customWidth="1"/>
-    <col min="3" max="5" width="8.81640625" style="20"/>
-    <col min="6" max="6" width="88.7265625" style="20" customWidth="1"/>
-    <col min="7" max="7" width="17.1796875" style="20" customWidth="1"/>
-    <col min="8" max="8" width="35.26953125" style="20" customWidth="1"/>
-    <col min="9" max="9" width="20.453125" style="20" customWidth="1"/>
-    <col min="10" max="10" width="33.453125" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="1" max="1" width="40.85546875" style="64" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" style="20" customWidth="1"/>
+    <col min="3" max="5" width="8.85546875" style="20"/>
+    <col min="6" max="6" width="88.7109375" style="20" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="35.28515625" style="20" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" style="20" customWidth="1"/>
+    <col min="10" max="10" width="33.42578125" style="20" customWidth="1"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="36" customFormat="1" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="36" customFormat="1" ht="42.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="121" t="s">
         <v>24</v>
       </c>
@@ -7737,8 +7733,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="388" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="165" t="s">
+    <row r="2" spans="1:10" ht="394.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="176" t="s">
         <v>814</v>
       </c>
       <c r="B2" s="122" t="s">
@@ -7763,8 +7759,8 @@
         <v>818</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="403.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="165"/>
+    <row r="3" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="176"/>
       <c r="B3" s="98" t="s">
         <v>819</v>
       </c>
@@ -7791,8 +7787,8 @@
         <v>823</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="357" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="165"/>
+    <row r="4" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="176"/>
       <c r="B4" s="98" t="s">
         <v>824</v>
       </c>
@@ -7819,8 +7815,8 @@
         <v>828</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="310.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="165"/>
+    <row r="5" spans="1:10" ht="315.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="176"/>
       <c r="B5" s="98" t="s">
         <v>829</v>
       </c>
@@ -7843,8 +7839,8 @@
         <v>832</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="295" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="165"/>
+    <row r="6" spans="1:10" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="176"/>
       <c r="B6" s="98" t="s">
         <v>833</v>
       </c>
@@ -7867,8 +7863,8 @@
         <v>836</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="372.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="164" t="s">
+    <row r="7" spans="1:10" ht="394.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="175" t="s">
         <v>837</v>
       </c>
       <c r="B7" s="98" t="s">
@@ -7897,8 +7893,8 @@
         <v>842</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="403.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="164"/>
+    <row r="8" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="175"/>
       <c r="B8" s="98" t="s">
         <v>843</v>
       </c>
@@ -7923,8 +7919,8 @@
         <v>846</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="233" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="164"/>
+    <row r="9" spans="1:10" ht="268.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="175"/>
       <c r="B9" s="98" t="s">
         <v>847</v>
       </c>
@@ -7949,8 +7945,8 @@
         <v>850</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="372.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="164"/>
+    <row r="10" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="175"/>
       <c r="B10" s="98" t="s">
         <v>851</v>
       </c>
@@ -7977,8 +7973,8 @@
         <v>855</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="310.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="164"/>
+    <row r="11" spans="1:10" ht="363" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="175"/>
       <c r="B11" s="98" t="s">
         <v>856</v>
       </c>
@@ -8001,8 +7997,8 @@
         <v>859</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="341.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="164"/>
+    <row r="12" spans="1:10" ht="378.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="175"/>
       <c r="B12" s="98" t="s">
         <v>860</v>
       </c>
@@ -8027,8 +8023,8 @@
         <v>863</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="164" t="s">
+    <row r="13" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="175" t="s">
         <v>864</v>
       </c>
       <c r="B13" s="98" t="s">
@@ -8051,8 +8047,8 @@
       <c r="I13" s="132"/>
       <c r="J13" s="133"/>
     </row>
-    <row r="14" spans="1:10" ht="310.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="164"/>
+    <row r="14" spans="1:10" ht="363" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="175"/>
       <c r="B14" s="98" t="s">
         <v>867</v>
       </c>
@@ -8079,8 +8075,8 @@
         <v>871</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="295" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="164"/>
+    <row r="15" spans="1:10" ht="331.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="175"/>
       <c r="B15" s="98" t="s">
         <v>872</v>
       </c>
@@ -8105,8 +8101,8 @@
         <v>875</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="403.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="164" t="s">
+    <row r="16" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="175" t="s">
         <v>876</v>
       </c>
       <c r="B16" s="98" t="s">
@@ -8135,8 +8131,8 @@
         <v>881</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="295" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="164"/>
+    <row r="17" spans="1:10" ht="363" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="175"/>
       <c r="B17" s="98" t="s">
         <v>882</v>
       </c>
@@ -8161,8 +8157,8 @@
         <v>885</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="279.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="164"/>
+    <row r="18" spans="1:10" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="175"/>
       <c r="B18" s="98" t="s">
         <v>886</v>
       </c>
@@ -8187,8 +8183,8 @@
         <v>889</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="248.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="164"/>
+    <row r="19" spans="1:10" ht="268.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="175"/>
       <c r="B19" s="98" t="s">
         <v>890</v>
       </c>
@@ -8213,8 +8209,8 @@
         <v>893</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="341.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="164"/>
+    <row r="20" spans="1:10" ht="363" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="175"/>
       <c r="B20" s="98" t="s">
         <v>894</v>
       </c>
@@ -8241,8 +8237,8 @@
         <v>898</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="248.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="164"/>
+    <row r="21" spans="1:10" ht="284.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="175"/>
       <c r="B21" s="98" t="s">
         <v>899</v>
       </c>
@@ -8267,8 +8263,8 @@
         <v>902</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="248.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="164"/>
+    <row r="22" spans="1:10" ht="284.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="175"/>
       <c r="B22" s="98" t="s">
         <v>903</v>
       </c>
@@ -8293,8 +8289,8 @@
         <v>906</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="326" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="164" t="s">
+    <row r="23" spans="1:10" ht="347.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="175" t="s">
         <v>907</v>
       </c>
       <c r="B23" s="98" t="s">
@@ -8321,8 +8317,8 @@
         <v>911</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="295" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="164"/>
+    <row r="24" spans="1:10" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="175"/>
       <c r="B24" s="98" t="s">
         <v>912</v>
       </c>
@@ -8349,8 +8345,8 @@
         <v>916</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="357" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="164"/>
+    <row r="25" spans="1:10" ht="363" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="175"/>
       <c r="B25" s="98" t="s">
         <v>917</v>
       </c>
@@ -8377,8 +8373,8 @@
         <v>921</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="341.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="164"/>
+    <row r="26" spans="1:10" ht="363" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="175"/>
       <c r="B26" s="98" t="s">
         <v>922</v>
       </c>
@@ -8429,19 +8425,19 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:AMJ16"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" style="64" customWidth="1"/>
-    <col min="2" max="5" width="8.81640625" style="20"/>
-    <col min="6" max="6" width="84.453125" style="20" customWidth="1"/>
-    <col min="7" max="7" width="17.54296875" style="20" customWidth="1"/>
-    <col min="8" max="8" width="35.453125" style="20" customWidth="1"/>
-    <col min="9" max="9" width="24.1796875" style="20" customWidth="1"/>
-    <col min="10" max="10" width="37.81640625" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="2" max="5" width="8.85546875" style="20"/>
+    <col min="6" max="6" width="84.42578125" style="20" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="35.42578125" style="20" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" style="20" customWidth="1"/>
+    <col min="10" max="10" width="37.85546875" style="20" customWidth="1"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="36" customFormat="1" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="36" customFormat="1" ht="42.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="75" t="s">
         <v>24</v>
       </c>
@@ -8477,8 +8473,8 @@
       <c r="M1" s="147"/>
       <c r="N1" s="147"/>
     </row>
-    <row r="2" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="163" t="s">
+    <row r="2" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="174" t="s">
         <v>780</v>
       </c>
       <c r="B2" s="37" t="s">
@@ -8507,8 +8503,8 @@
         <v>926</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="163"/>
+    <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="174"/>
       <c r="B3" s="37" t="s">
         <v>783</v>
       </c>
@@ -8529,8 +8525,8 @@
       <c r="I3" s="24"/>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:14" ht="217" x14ac:dyDescent="0.35">
-      <c r="A4" s="163"/>
+    <row r="4" spans="1:14" ht="252" x14ac:dyDescent="0.25">
+      <c r="A4" s="174"/>
       <c r="B4" s="37" t="s">
         <v>785</v>
       </c>
@@ -8557,8 +8553,8 @@
         <v>929</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="341" x14ac:dyDescent="0.35">
-      <c r="A5" s="163"/>
+    <row r="5" spans="1:14" ht="362.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="174"/>
       <c r="B5" s="37" t="s">
         <v>787</v>
       </c>
@@ -8585,8 +8581,8 @@
         <v>931</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="263.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="163"/>
+    <row r="6" spans="1:14" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="174"/>
       <c r="B6" s="37" t="s">
         <v>789</v>
       </c>
@@ -8609,8 +8605,8 @@
       </c>
       <c r="J6" s="25"/>
     </row>
-    <row r="7" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="163" t="s">
+    <row r="7" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="174" t="s">
         <v>791</v>
       </c>
       <c r="B7" s="37" t="s">
@@ -8637,8 +8633,8 @@
         <v>933</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="248" x14ac:dyDescent="0.35">
-      <c r="A8" s="163"/>
+    <row r="8" spans="1:14" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="174"/>
       <c r="B8" s="37" t="s">
         <v>794</v>
       </c>
@@ -8661,8 +8657,8 @@
       </c>
       <c r="J8" s="25"/>
     </row>
-    <row r="9" spans="1:14" ht="248" x14ac:dyDescent="0.35">
-      <c r="A9" s="163"/>
+    <row r="9" spans="1:14" ht="267.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="174"/>
       <c r="B9" s="37" t="s">
         <v>796</v>
       </c>
@@ -8685,8 +8681,8 @@
       </c>
       <c r="J9" s="25"/>
     </row>
-    <row r="10" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="163"/>
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="174"/>
       <c r="B10" s="37" t="s">
         <v>798</v>
       </c>
@@ -8707,8 +8703,8 @@
       <c r="I10" s="24"/>
       <c r="J10" s="25"/>
     </row>
-    <row r="11" spans="1:14" ht="186" x14ac:dyDescent="0.35">
-      <c r="A11" s="163"/>
+    <row r="11" spans="1:14" ht="220.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="174"/>
       <c r="B11" s="37" t="s">
         <v>800</v>
       </c>
@@ -8731,8 +8727,8 @@
       </c>
       <c r="J11" s="25"/>
     </row>
-    <row r="12" spans="1:14" ht="232.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="163"/>
+    <row r="12" spans="1:14" ht="236.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="174"/>
       <c r="B12" s="37" t="s">
         <v>802</v>
       </c>
@@ -8759,8 +8755,8 @@
         <v>939</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="163" t="s">
+    <row r="13" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="174" t="s">
         <v>804</v>
       </c>
       <c r="B13" s="37" t="s">
@@ -8785,8 +8781,8 @@
       </c>
       <c r="J13" s="25"/>
     </row>
-    <row r="14" spans="1:14" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="163"/>
+    <row r="14" spans="1:14" ht="126" x14ac:dyDescent="0.25">
+      <c r="A14" s="174"/>
       <c r="B14" s="37" t="s">
         <v>807</v>
       </c>
@@ -8809,8 +8805,8 @@
       </c>
       <c r="J14" s="25"/>
     </row>
-    <row r="15" spans="1:14" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="163" t="s">
+    <row r="15" spans="1:14" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="174" t="s">
         <v>809</v>
       </c>
       <c r="B15" s="37" t="s">
@@ -8835,8 +8831,8 @@
       </c>
       <c r="J15" s="25"/>
     </row>
-    <row r="16" spans="1:14" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="163"/>
+    <row r="16" spans="1:14" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="174"/>
       <c r="B16" s="37" t="s">
         <v>812</v>
       </c>
@@ -8884,21 +8880,21 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AMJ11"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.26953125" style="64" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" style="20"/>
-    <col min="3" max="4" width="8.81640625" style="52"/>
-    <col min="5" max="5" width="9.453125" style="52" customWidth="1"/>
+    <col min="1" max="1" width="31.28515625" style="64" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="20"/>
+    <col min="3" max="4" width="8.85546875" style="52"/>
+    <col min="5" max="5" width="9.42578125" style="52" customWidth="1"/>
     <col min="6" max="6" width="106" style="20" customWidth="1"/>
-    <col min="7" max="7" width="8.81640625" style="20"/>
-    <col min="8" max="8" width="35.81640625" style="20" customWidth="1"/>
-    <col min="9" max="9" width="26.1796875" style="20" customWidth="1"/>
-    <col min="10" max="10" width="28.7265625" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="7" max="7" width="8.85546875" style="20"/>
+    <col min="8" max="8" width="35.85546875" style="20" customWidth="1"/>
+    <col min="9" max="9" width="26.140625" style="20" customWidth="1"/>
+    <col min="10" max="10" width="28.7109375" style="20" customWidth="1"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.2">
       <c r="A1" s="76" t="s">
         <v>24</v>
       </c>
@@ -8930,7 +8926,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="186" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="220.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>704</v>
       </c>
@@ -8956,8 +8952,8 @@
       </c>
       <c r="J2" s="44"/>
     </row>
-    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="163" t="s">
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="174" t="s">
         <v>707</v>
       </c>
       <c r="B3" s="37" t="s">
@@ -8986,8 +8982,8 @@
         <v>952</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="163"/>
+    <row r="4" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="174"/>
       <c r="B4" s="37" t="s">
         <v>710</v>
       </c>
@@ -9014,8 +9010,8 @@
         <v>953</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="186" x14ac:dyDescent="0.35">
-      <c r="A5" s="163"/>
+    <row r="5" spans="1:10" ht="189" x14ac:dyDescent="0.25">
+      <c r="A5" s="174"/>
       <c r="B5" s="37" t="s">
         <v>712</v>
       </c>
@@ -9042,8 +9038,8 @@
         <v>957</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="163"/>
+    <row r="6" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="174"/>
       <c r="B6" s="37" t="s">
         <v>714</v>
       </c>
@@ -9070,8 +9066,8 @@
         <v>956</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="186" x14ac:dyDescent="0.35">
-      <c r="A7" s="163"/>
+    <row r="7" spans="1:10" ht="204.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="174"/>
       <c r="B7" s="37" t="s">
         <v>716</v>
       </c>
@@ -9098,8 +9094,8 @@
         <v>962</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="155" x14ac:dyDescent="0.35">
-      <c r="A8" s="163"/>
+    <row r="8" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="174"/>
       <c r="B8" s="37" t="s">
         <v>718</v>
       </c>
@@ -9126,8 +9122,8 @@
         <v>965</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="163" t="s">
+    <row r="9" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="174" t="s">
         <v>720</v>
       </c>
       <c r="B9" s="37" t="s">
@@ -9152,8 +9148,8 @@
       </c>
       <c r="J9" s="25"/>
     </row>
-    <row r="10" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="163"/>
+    <row r="10" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="174"/>
       <c r="B10" s="37" t="s">
         <v>723</v>
       </c>
@@ -9178,8 +9174,8 @@
         <v>968</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="163"/>
+    <row r="11" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="174"/>
       <c r="B11" s="37" t="s">
         <v>725</v>
       </c>
@@ -9225,20 +9221,20 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:AMJ9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.81640625" style="64" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" style="20"/>
-    <col min="3" max="5" width="8.81640625" style="52"/>
-    <col min="6" max="6" width="71.26953125" style="20" customWidth="1"/>
-    <col min="7" max="7" width="17.453125" style="20" customWidth="1"/>
-    <col min="8" max="8" width="34.7265625" style="20" customWidth="1"/>
-    <col min="9" max="9" width="34.453125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" style="64" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="20"/>
+    <col min="3" max="5" width="8.85546875" style="52"/>
+    <col min="6" max="6" width="71.28515625" style="20" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="34.7109375" style="20" customWidth="1"/>
+    <col min="9" max="9" width="34.42578125" style="20" customWidth="1"/>
     <col min="10" max="10" width="37" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.2">
       <c r="A1" s="75" t="s">
         <v>24</v>
       </c>
@@ -9270,8 +9266,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="163" t="s">
+    <row r="2" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="174" t="s">
         <v>727</v>
       </c>
       <c r="B2" s="37" t="s">
@@ -9296,8 +9292,8 @@
       </c>
       <c r="J2" s="44"/>
     </row>
-    <row r="3" spans="1:10" ht="155" x14ac:dyDescent="0.35">
-      <c r="A3" s="163"/>
+    <row r="3" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="174"/>
       <c r="B3" s="37" t="s">
         <v>730</v>
       </c>
@@ -9320,8 +9316,8 @@
       </c>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:10" ht="155" x14ac:dyDescent="0.35">
-      <c r="A4" s="163"/>
+    <row r="4" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="174"/>
       <c r="B4" s="37" t="s">
         <v>732</v>
       </c>
@@ -9344,8 +9340,8 @@
       </c>
       <c r="J4" s="25"/>
     </row>
-    <row r="5" spans="1:10" ht="124" x14ac:dyDescent="0.35">
-      <c r="A5" s="163"/>
+    <row r="5" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="174"/>
       <c r="B5" s="37" t="s">
         <v>734</v>
       </c>
@@ -9368,8 +9364,8 @@
       </c>
       <c r="J5" s="25"/>
     </row>
-    <row r="6" spans="1:10" ht="155" x14ac:dyDescent="0.35">
-      <c r="A6" s="163"/>
+    <row r="6" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="174"/>
       <c r="B6" s="37" t="s">
         <v>736</v>
       </c>
@@ -9383,7 +9379,7 @@
       <c r="F6" s="72" t="s">
         <v>737</v>
       </c>
-      <c r="G6" s="167" t="s">
+      <c r="G6" s="163" t="s">
         <v>30</v>
       </c>
       <c r="H6" s="24" t="s">
@@ -9394,8 +9390,8 @@
       </c>
       <c r="J6" s="25"/>
     </row>
-    <row r="7" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="163"/>
+    <row r="7" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="174"/>
       <c r="B7" s="37" t="s">
         <v>738</v>
       </c>
@@ -9418,8 +9414,8 @@
       </c>
       <c r="J7" s="25"/>
     </row>
-    <row r="8" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="163"/>
+    <row r="8" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="174"/>
       <c r="B8" s="37" t="s">
         <v>740</v>
       </c>
@@ -9433,7 +9429,7 @@
       <c r="F8" s="72" t="s">
         <v>741</v>
       </c>
-      <c r="G8" s="167" t="s">
+      <c r="G8" s="163" t="s">
         <v>30</v>
       </c>
       <c r="H8" s="24" t="s">
@@ -9444,8 +9440,8 @@
       </c>
       <c r="J8" s="25"/>
     </row>
-    <row r="9" spans="1:10" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="163"/>
+    <row r="9" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="174"/>
       <c r="B9" s="37" t="s">
         <v>742</v>
       </c>
@@ -9490,20 +9486,20 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:AMJ16"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" style="64" customWidth="1"/>
-    <col min="2" max="2" width="13.26953125" style="20" customWidth="1"/>
-    <col min="3" max="5" width="8.81640625" style="52"/>
-    <col min="6" max="6" width="78.7265625" style="20" customWidth="1"/>
-    <col min="7" max="7" width="18.81640625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="31.453125" style="20" customWidth="1"/>
-    <col min="9" max="9" width="26.81640625" style="20" customWidth="1"/>
-    <col min="10" max="10" width="31.81640625" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="1" max="1" width="33.5703125" style="64" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" style="20" customWidth="1"/>
+    <col min="3" max="5" width="8.85546875" style="52"/>
+    <col min="6" max="6" width="78.7109375" style="20" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" style="20" customWidth="1"/>
+    <col min="8" max="8" width="31.42578125" style="20" customWidth="1"/>
+    <col min="9" max="9" width="26.85546875" style="20" customWidth="1"/>
+    <col min="10" max="10" width="31.85546875" style="20" customWidth="1"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.2">
       <c r="A1" s="75" t="s">
         <v>24</v>
       </c>
@@ -9535,8 +9531,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="163" t="s">
+    <row r="2" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="174" t="s">
         <v>744</v>
       </c>
       <c r="B2" s="37" t="s">
@@ -9561,8 +9557,8 @@
       </c>
       <c r="J2" s="44"/>
     </row>
-    <row r="3" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="163"/>
+    <row r="3" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="174"/>
       <c r="B3" s="37" t="s">
         <v>747</v>
       </c>
@@ -9585,8 +9581,8 @@
       </c>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:10" ht="124" x14ac:dyDescent="0.35">
-      <c r="A4" s="163"/>
+    <row r="4" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="174"/>
       <c r="B4" s="37" t="s">
         <v>749</v>
       </c>
@@ -9609,7 +9605,7 @@
       </c>
       <c r="J4" s="25"/>
     </row>
-    <row r="5" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>751</v>
       </c>
@@ -9639,8 +9635,8 @@
         <v>983</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="163" t="s">
+    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="174" t="s">
         <v>754</v>
       </c>
       <c r="B6" s="37" t="s">
@@ -9665,8 +9661,8 @@
       </c>
       <c r="J6" s="25"/>
     </row>
-    <row r="7" spans="1:10" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="163"/>
+    <row r="7" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="174"/>
       <c r="B7" s="37" t="s">
         <v>757</v>
       </c>
@@ -9689,8 +9685,8 @@
       </c>
       <c r="J7" s="25"/>
     </row>
-    <row r="8" spans="1:10" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="163"/>
+    <row r="8" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="174"/>
       <c r="B8" s="37" t="s">
         <v>759</v>
       </c>
@@ -9713,8 +9709,8 @@
       </c>
       <c r="J8" s="25"/>
     </row>
-    <row r="9" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="163"/>
+    <row r="9" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="174"/>
       <c r="B9" s="37" t="s">
         <v>761</v>
       </c>
@@ -9739,8 +9735,8 @@
       </c>
       <c r="J9" s="25"/>
     </row>
-    <row r="10" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="163"/>
+    <row r="10" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="174"/>
       <c r="B10" s="37" t="s">
         <v>763</v>
       </c>
@@ -9767,8 +9763,8 @@
         <v>991</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="163"/>
+    <row r="11" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="174"/>
       <c r="B11" s="37" t="s">
         <v>765</v>
       </c>
@@ -9793,8 +9789,8 @@
         <v>994</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="163" t="s">
+    <row r="12" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="174" t="s">
         <v>767</v>
       </c>
       <c r="B12" s="37" t="s">
@@ -9823,8 +9819,8 @@
         <v>996</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="163"/>
+    <row r="13" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="174"/>
       <c r="B13" s="37" t="s">
         <v>770</v>
       </c>
@@ -9847,8 +9843,8 @@
       </c>
       <c r="J13" s="25"/>
     </row>
-    <row r="14" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="163" t="s">
+    <row r="14" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="174" t="s">
         <v>772</v>
       </c>
       <c r="B14" s="37" t="s">
@@ -9873,8 +9869,8 @@
       </c>
       <c r="J14" s="25"/>
     </row>
-    <row r="15" spans="1:10" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="163"/>
+    <row r="15" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="174"/>
       <c r="B15" s="37" t="s">
         <v>775</v>
       </c>
@@ -9899,7 +9895,7 @@
       </c>
       <c r="J15" s="150"/>
     </row>
-    <row r="16" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>777</v>
       </c>
@@ -9950,21 +9946,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AMJ45"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.453125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" style="14"/>
-    <col min="3" max="3" width="10.7265625" style="14" customWidth="1"/>
-    <col min="4" max="5" width="8.81640625" style="14"/>
-    <col min="6" max="6" width="60.81640625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="19.1796875" style="14" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="14"/>
+    <col min="3" max="3" width="10.7109375" style="14" customWidth="1"/>
+    <col min="4" max="5" width="8.85546875" style="14"/>
+    <col min="6" max="6" width="60.85546875" style="14" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" style="14" customWidth="1"/>
     <col min="8" max="8" width="36" style="14" customWidth="1"/>
-    <col min="9" max="9" width="31.7265625" style="14" customWidth="1"/>
-    <col min="10" max="10" width="41.7265625" style="14" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="14"/>
+    <col min="9" max="9" width="31.7109375" style="14" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" style="14" customWidth="1"/>
+    <col min="11" max="1024" width="8.85546875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" ht="42.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="42.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="153" t="s">
         <v>24</v>
       </c>
@@ -9996,8 +9992,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="20" customFormat="1" ht="310.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="162" t="s">
+    <row r="2" spans="1:10" s="20" customFormat="1" ht="347.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="173" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="154" t="s">
@@ -10017,13 +10013,13 @@
       <c r="H2" s="18" t="s">
         <v>1173</v>
       </c>
-      <c r="I2" s="166" t="s">
+      <c r="I2" s="162" t="s">
         <v>1145</v>
       </c>
       <c r="J2" s="19"/>
     </row>
-    <row r="3" spans="1:10" s="20" customFormat="1" ht="124.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="162"/>
+    <row r="3" spans="1:10" s="20" customFormat="1" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="173"/>
       <c r="B3" s="154" t="s">
         <v>37</v>
       </c>
@@ -10048,8 +10044,8 @@
       </c>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:10" s="20" customFormat="1" ht="186.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="162"/>
+    <row r="4" spans="1:10" s="20" customFormat="1" ht="205.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="173"/>
       <c r="B4" s="154" t="s">
         <v>39</v>
       </c>
@@ -10076,8 +10072,8 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="20" customFormat="1" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="162"/>
+    <row r="5" spans="1:10" s="20" customFormat="1" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="173"/>
       <c r="B5" s="154" t="s">
         <v>41</v>
       </c>
@@ -10104,8 +10100,8 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="20" customFormat="1" ht="186" x14ac:dyDescent="0.35">
-      <c r="A6" s="162"/>
+    <row r="6" spans="1:10" s="20" customFormat="1" ht="204.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="173"/>
       <c r="B6" s="154" t="s">
         <v>43</v>
       </c>
@@ -10130,8 +10126,8 @@
       </c>
       <c r="J6" s="25"/>
     </row>
-    <row r="7" spans="1:10" s="20" customFormat="1" ht="124" x14ac:dyDescent="0.35">
-      <c r="A7" s="162"/>
+    <row r="7" spans="1:10" s="20" customFormat="1" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="173"/>
       <c r="B7" s="154" t="s">
         <v>45</v>
       </c>
@@ -10156,8 +10152,8 @@
       </c>
       <c r="J7" s="25"/>
     </row>
-    <row r="8" spans="1:10" s="20" customFormat="1" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="162"/>
+    <row r="8" spans="1:10" s="20" customFormat="1" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="173"/>
       <c r="B8" s="154" t="s">
         <v>47</v>
       </c>
@@ -10184,8 +10180,8 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="20" customFormat="1" ht="202" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="162" t="s">
+    <row r="9" spans="1:10" s="20" customFormat="1" ht="221.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="173" t="s">
         <v>49</v>
       </c>
       <c r="B9" s="154" t="s">
@@ -10204,7 +10200,7 @@
       <c r="G9" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="167" t="s">
+      <c r="H9" s="163" t="s">
         <v>1158</v>
       </c>
       <c r="I9" s="24" t="s">
@@ -10212,8 +10208,8 @@
       </c>
       <c r="J9" s="25"/>
     </row>
-    <row r="10" spans="1:10" s="20" customFormat="1" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="162"/>
+    <row r="10" spans="1:10" s="20" customFormat="1" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="173"/>
       <c r="B10" s="154" t="s">
         <v>52</v>
       </c>
@@ -10238,8 +10234,8 @@
       </c>
       <c r="J10" s="25"/>
     </row>
-    <row r="11" spans="1:10" s="20" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="162"/>
+    <row r="11" spans="1:10" s="20" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="173"/>
       <c r="B11" s="154" t="s">
         <v>54</v>
       </c>
@@ -10256,7 +10252,7 @@
       <c r="G11" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="168" t="s">
+      <c r="H11" s="164" t="s">
         <v>1168</v>
       </c>
       <c r="I11" s="24" t="s">
@@ -10266,8 +10262,8 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="20" customFormat="1" ht="328" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="162"/>
+    <row r="12" spans="1:10" s="20" customFormat="1" ht="327.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="173"/>
       <c r="B12" s="154" t="s">
         <v>56</v>
       </c>
@@ -10294,7 +10290,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="20" customFormat="1" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" s="20" customFormat="1" ht="42.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>58</v>
       </c>
@@ -10312,8 +10308,8 @@
       <c r="I13" s="24"/>
       <c r="J13" s="25"/>
     </row>
-    <row r="14" spans="1:10" s="20" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="162" t="s">
+    <row r="14" spans="1:10" s="20" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="173" t="s">
         <v>61</v>
       </c>
       <c r="B14" s="154" t="s">
@@ -10342,8 +10338,8 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="20" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="162"/>
+    <row r="15" spans="1:10" s="20" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="173"/>
       <c r="B15" s="154" t="s">
         <v>64</v>
       </c>
@@ -10364,8 +10360,8 @@
       <c r="I15" s="24"/>
       <c r="J15" s="25"/>
     </row>
-    <row r="16" spans="1:10" s="20" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="162"/>
+    <row r="16" spans="1:10" s="20" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="173"/>
       <c r="B16" s="154" t="s">
         <v>66</v>
       </c>
@@ -10386,8 +10382,8 @@
       <c r="I16" s="24"/>
       <c r="J16" s="25"/>
     </row>
-    <row r="17" spans="1:10" s="20" customFormat="1" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="162"/>
+    <row r="17" spans="1:10" s="20" customFormat="1" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="173"/>
       <c r="B17" s="154" t="s">
         <v>68</v>
       </c>
@@ -10414,8 +10410,8 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="20" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="162"/>
+    <row r="18" spans="1:10" s="20" customFormat="1" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="173"/>
       <c r="B18" s="154" t="s">
         <v>70</v>
       </c>
@@ -10442,8 +10438,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="20" customFormat="1" ht="78" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="162" t="s">
+    <row r="19" spans="1:10" s="20" customFormat="1" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="173" t="s">
         <v>72</v>
       </c>
       <c r="B19" s="154" t="s">
@@ -10472,8 +10468,8 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="20" customFormat="1" ht="119.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="162"/>
+    <row r="20" spans="1:10" s="20" customFormat="1" ht="119.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="173"/>
       <c r="B20" s="154" t="s">
         <v>75</v>
       </c>
@@ -10500,8 +10496,8 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="20" customFormat="1" ht="171" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="162"/>
+    <row r="21" spans="1:10" s="20" customFormat="1" ht="189.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="173"/>
       <c r="B21" s="154" t="s">
         <v>77</v>
       </c>
@@ -10526,8 +10522,8 @@
       </c>
       <c r="J21" s="25"/>
     </row>
-    <row r="22" spans="1:10" s="20" customFormat="1" ht="78.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="162"/>
+    <row r="22" spans="1:10" s="20" customFormat="1" ht="78.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="173"/>
       <c r="B22" s="154" t="s">
         <v>79</v>
       </c>
@@ -10552,8 +10548,8 @@
       </c>
       <c r="J22" s="25"/>
     </row>
-    <row r="23" spans="1:10" s="20" customFormat="1" ht="141.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="162" t="s">
+    <row r="23" spans="1:10" s="20" customFormat="1" ht="141.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="173" t="s">
         <v>81</v>
       </c>
       <c r="B23" s="154" t="s">
@@ -10572,7 +10568,7 @@
       <c r="G23" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="H23" s="170" t="s">
+      <c r="H23" s="166" t="s">
         <v>1198</v>
       </c>
       <c r="I23" s="24" t="s">
@@ -10582,8 +10578,8 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="20" customFormat="1" ht="171" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="162"/>
+    <row r="24" spans="1:10" s="20" customFormat="1" ht="174" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="173"/>
       <c r="B24" s="154" t="s">
         <v>84</v>
       </c>
@@ -10600,7 +10596,7 @@
       <c r="G24" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="H24" s="171" t="s">
+      <c r="H24" s="167" t="s">
         <v>1199</v>
       </c>
       <c r="I24" s="24" t="s">
@@ -10610,8 +10606,8 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="20" customFormat="1" ht="171" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="162"/>
+    <row r="25" spans="1:10" s="20" customFormat="1" ht="189.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="173"/>
       <c r="B25" s="154" t="s">
         <v>86</v>
       </c>
@@ -10628,7 +10624,7 @@
       <c r="G25" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="H25" s="171" t="s">
+      <c r="H25" s="167" t="s">
         <v>1200</v>
       </c>
       <c r="I25" s="24" t="s">
@@ -10638,8 +10634,8 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="20" customFormat="1" ht="62.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="162"/>
+    <row r="26" spans="1:10" s="20" customFormat="1" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="173"/>
       <c r="B26" s="154" t="s">
         <v>88</v>
       </c>
@@ -10666,8 +10662,8 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="20" customFormat="1" ht="107" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="162" t="s">
+    <row r="27" spans="1:10" s="20" customFormat="1" ht="107.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="173" t="s">
         <v>90</v>
       </c>
       <c r="B27" s="154" t="s">
@@ -10686,7 +10682,7 @@
       <c r="G27" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="H27" s="170" t="s">
+      <c r="H27" s="166" t="s">
         <v>1204</v>
       </c>
       <c r="I27" s="24" t="s">
@@ -10696,8 +10692,8 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="20" customFormat="1" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="162"/>
+    <row r="28" spans="1:10" s="20" customFormat="1" ht="111" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="173"/>
       <c r="B28" s="154" t="s">
         <v>93</v>
       </c>
@@ -10712,7 +10708,7 @@
       <c r="G28" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="H28" s="171" t="s">
+      <c r="H28" s="167" t="s">
         <v>1205</v>
       </c>
       <c r="I28" s="24" t="s">
@@ -10722,8 +10718,8 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="20" customFormat="1" ht="78" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="162" t="s">
+    <row r="29" spans="1:10" s="20" customFormat="1" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="173" t="s">
         <v>95</v>
       </c>
       <c r="B29" s="154" t="s">
@@ -10750,8 +10746,8 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="20" customFormat="1" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="162"/>
+    <row r="30" spans="1:10" s="20" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="173"/>
       <c r="B30" s="154" t="s">
         <v>98</v>
       </c>
@@ -10776,8 +10772,8 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="31" spans="1:10" s="20" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="162" t="s">
+    <row r="31" spans="1:10" s="20" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="173" t="s">
         <v>100</v>
       </c>
       <c r="B31" s="154" t="s">
@@ -10804,8 +10800,8 @@
       </c>
       <c r="J31" s="25"/>
     </row>
-    <row r="32" spans="1:10" s="20" customFormat="1" ht="62" x14ac:dyDescent="0.35">
-      <c r="A32" s="162"/>
+    <row r="32" spans="1:10" s="20" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+      <c r="A32" s="173"/>
       <c r="B32" s="154" t="s">
         <v>103</v>
       </c>
@@ -10830,7 +10826,7 @@
       </c>
       <c r="J32" s="25"/>
     </row>
-    <row r="33" spans="1:10" s="20" customFormat="1" ht="140" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:10" s="20" customFormat="1" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>105</v>
       </c>
@@ -10858,8 +10854,8 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="20" customFormat="1" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="162" t="s">
+    <row r="34" spans="1:10" s="20" customFormat="1" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="173" t="s">
         <v>108</v>
       </c>
       <c r="B34" s="154" t="s">
@@ -10886,8 +10882,8 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="20" customFormat="1" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="162"/>
+    <row r="35" spans="1:10" s="20" customFormat="1" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="173"/>
       <c r="B35" s="154" t="s">
         <v>111</v>
       </c>
@@ -10914,8 +10910,8 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="20" customFormat="1" ht="93" x14ac:dyDescent="0.35">
-      <c r="A36" s="162"/>
+    <row r="36" spans="1:10" s="20" customFormat="1" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="173"/>
       <c r="B36" s="154" t="s">
         <v>113</v>
       </c>
@@ -10942,8 +10938,8 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="37" spans="1:10" s="20" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="162" t="s">
+    <row r="37" spans="1:10" s="20" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="173" t="s">
         <v>115</v>
       </c>
       <c r="B37" s="154" t="s">
@@ -10966,8 +10962,8 @@
       <c r="I37" s="24"/>
       <c r="J37" s="25"/>
     </row>
-    <row r="38" spans="1:10" s="20" customFormat="1" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="162"/>
+    <row r="38" spans="1:10" s="20" customFormat="1" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="173"/>
       <c r="B38" s="154" t="s">
         <v>118</v>
       </c>
@@ -10992,7 +10988,7 @@
       </c>
       <c r="J38" s="25"/>
     </row>
-    <row r="39" spans="1:10" s="20" customFormat="1" ht="21.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:10" s="20" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>120</v>
       </c>
@@ -11010,8 +11006,8 @@
       <c r="I39" s="24"/>
       <c r="J39" s="25"/>
     </row>
-    <row r="40" spans="1:10" s="20" customFormat="1" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="162" t="s">
+    <row r="40" spans="1:10" s="20" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="173" t="s">
         <v>121</v>
       </c>
       <c r="B40" s="154" t="s">
@@ -11036,8 +11032,8 @@
       </c>
       <c r="J40" s="25"/>
     </row>
-    <row r="41" spans="1:10" s="20" customFormat="1" ht="62" x14ac:dyDescent="0.35">
-      <c r="A41" s="162"/>
+    <row r="41" spans="1:10" s="20" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="173"/>
       <c r="B41" s="154" t="s">
         <v>124</v>
       </c>
@@ -11064,8 +11060,8 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="42" spans="1:10" s="20" customFormat="1" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="162"/>
+    <row r="42" spans="1:10" s="20" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="173"/>
       <c r="B42" s="154" t="s">
         <v>126</v>
       </c>
@@ -11092,8 +11088,8 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="20" customFormat="1" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="162"/>
+    <row r="43" spans="1:10" s="20" customFormat="1" ht="189" x14ac:dyDescent="0.25">
+      <c r="A43" s="173"/>
       <c r="B43" s="154" t="s">
         <v>128</v>
       </c>
@@ -11108,7 +11104,7 @@
       <c r="G43" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="H43" s="171" t="s">
+      <c r="H43" s="167" t="s">
         <v>1234</v>
       </c>
       <c r="I43" s="24" t="s">
@@ -11118,8 +11114,8 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="20" customFormat="1" ht="93" x14ac:dyDescent="0.35">
-      <c r="A44" s="162"/>
+    <row r="44" spans="1:10" s="20" customFormat="1" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="173"/>
       <c r="B44" s="154" t="s">
         <v>130</v>
       </c>
@@ -11144,8 +11140,8 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="20" customFormat="1" ht="62" x14ac:dyDescent="0.35">
-      <c r="A45" s="162"/>
+    <row r="45" spans="1:10" s="20" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+      <c r="A45" s="173"/>
       <c r="B45" s="154" t="s">
         <v>132</v>
       </c>
@@ -11172,17 +11168,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:A8"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A26"/>
     <mergeCell ref="A40:A45"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A34:A36"/>
     <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" showErrorMessage="1" sqref="G2:G45" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -11202,21 +11198,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AMJ58"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.26953125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" style="31"/>
-    <col min="3" max="3" width="14.81640625" style="32" customWidth="1"/>
-    <col min="4" max="5" width="8.81640625" style="32"/>
+    <col min="1" max="1" width="34.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="31"/>
+    <col min="3" max="3" width="14.85546875" style="32" customWidth="1"/>
+    <col min="4" max="5" width="8.85546875" style="32"/>
     <col min="6" max="6" width="73" style="14" customWidth="1"/>
-    <col min="7" max="7" width="25.453125" style="14" customWidth="1"/>
-    <col min="8" max="8" width="30.26953125" style="14" customWidth="1"/>
-    <col min="9" max="9" width="33.453125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" style="14" customWidth="1"/>
+    <col min="8" max="8" width="30.28515625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="33.42578125" style="14" customWidth="1"/>
     <col min="10" max="10" width="29" style="14" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="14"/>
+    <col min="11" max="1024" width="8.85546875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="36" customFormat="1" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="36" customFormat="1" ht="42.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
         <v>24</v>
       </c>
@@ -11248,8 +11244,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="20" customFormat="1" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="163" t="s">
+    <row r="2" spans="1:10" s="20" customFormat="1" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="174" t="s">
         <v>1136</v>
       </c>
       <c r="B2" s="37" t="s">
@@ -11267,7 +11263,7 @@
       <c r="F2" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="G2" s="173" t="s">
+      <c r="G2" s="169" t="s">
         <v>30</v>
       </c>
       <c r="H2" s="43" t="s">
@@ -11280,8 +11276,8 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="20" customFormat="1" ht="279.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="163"/>
+    <row r="3" spans="1:10" s="20" customFormat="1" ht="315.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="174"/>
       <c r="B3" s="37" t="s">
         <v>137</v>
       </c>
@@ -11297,7 +11293,7 @@
       <c r="F3" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="169" t="s">
+      <c r="G3" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H3" s="24" t="s">
@@ -11310,8 +11306,8 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="20" customFormat="1" ht="341" x14ac:dyDescent="0.35">
-      <c r="A4" s="163"/>
+    <row r="4" spans="1:10" s="20" customFormat="1" ht="362.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="174"/>
       <c r="B4" s="37" t="s">
         <v>139</v>
       </c>
@@ -11327,7 +11323,7 @@
       <c r="F4" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="G4" s="169" t="s">
+      <c r="G4" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H4" s="24" t="s">
@@ -11340,8 +11336,8 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="20" customFormat="1" ht="217" x14ac:dyDescent="0.35">
-      <c r="A5" s="163"/>
+    <row r="5" spans="1:10" s="20" customFormat="1" ht="252" x14ac:dyDescent="0.25">
+      <c r="A5" s="174"/>
       <c r="B5" s="37" t="s">
         <v>141</v>
       </c>
@@ -11357,7 +11353,7 @@
       <c r="F5" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="169" t="s">
+      <c r="G5" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H5" s="24" t="s">
@@ -11370,8 +11366,8 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="20" customFormat="1" ht="213.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="163"/>
+    <row r="6" spans="1:10" s="20" customFormat="1" ht="230.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="174"/>
       <c r="B6" s="37" t="s">
         <v>143</v>
       </c>
@@ -11387,7 +11383,7 @@
       <c r="F6" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="G6" s="169" t="s">
+      <c r="G6" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H6" s="24" t="s">
@@ -11400,8 +11396,8 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="20" customFormat="1" ht="238.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="163"/>
+    <row r="7" spans="1:10" s="20" customFormat="1" ht="255.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="174"/>
       <c r="B7" s="37" t="s">
         <v>145</v>
       </c>
@@ -11417,7 +11413,7 @@
       <c r="F7" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="G7" s="169" t="s">
+      <c r="G7" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -11430,8 +11426,8 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="20" customFormat="1" ht="341" x14ac:dyDescent="0.35">
-      <c r="A8" s="163"/>
+    <row r="8" spans="1:10" s="20" customFormat="1" ht="362.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="174"/>
       <c r="B8" s="37" t="s">
         <v>147</v>
       </c>
@@ -11458,8 +11454,8 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="20" customFormat="1" ht="310" x14ac:dyDescent="0.35">
-      <c r="A9" s="163"/>
+    <row r="9" spans="1:10" s="20" customFormat="1" ht="330.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="174"/>
       <c r="B9" s="37" t="s">
         <v>149</v>
       </c>
@@ -11486,8 +11482,8 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="20" customFormat="1" ht="356.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="163"/>
+    <row r="10" spans="1:10" s="20" customFormat="1" ht="378" x14ac:dyDescent="0.25">
+      <c r="A10" s="174"/>
       <c r="B10" s="37" t="s">
         <v>151</v>
       </c>
@@ -11514,8 +11510,8 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="20" customFormat="1" ht="341" x14ac:dyDescent="0.35">
-      <c r="A11" s="163"/>
+    <row r="11" spans="1:10" s="20" customFormat="1" ht="378" x14ac:dyDescent="0.25">
+      <c r="A11" s="174"/>
       <c r="B11" s="37" t="s">
         <v>153</v>
       </c>
@@ -11542,8 +11538,8 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="20" customFormat="1" ht="251" x14ac:dyDescent="0.35">
-      <c r="A12" s="163"/>
+    <row r="12" spans="1:10" s="20" customFormat="1" ht="268.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="174"/>
       <c r="B12" s="37" t="s">
         <v>155</v>
       </c>
@@ -11570,8 +11566,8 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="20" customFormat="1" ht="356.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="163"/>
+    <row r="13" spans="1:10" s="20" customFormat="1" ht="378" x14ac:dyDescent="0.25">
+      <c r="A13" s="174"/>
       <c r="B13" s="37" t="s">
         <v>157</v>
       </c>
@@ -11598,8 +11594,8 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="20" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="163" t="s">
+    <row r="14" spans="1:10" s="20" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="174" t="s">
         <v>1141</v>
       </c>
       <c r="B14" s="37" t="s">
@@ -11617,7 +11613,7 @@
       <c r="F14" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="G14" s="169" t="s">
+      <c r="G14" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H14" s="24" t="s">
@@ -11630,8 +11626,8 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="20" customFormat="1" ht="325.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="163"/>
+    <row r="15" spans="1:10" s="20" customFormat="1" ht="346.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="174"/>
       <c r="B15" s="37" t="s">
         <v>162</v>
       </c>
@@ -11658,8 +11654,8 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="20" customFormat="1" ht="356.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="163"/>
+    <row r="16" spans="1:10" s="20" customFormat="1" ht="393.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="174"/>
       <c r="B16" s="37" t="s">
         <v>165</v>
       </c>
@@ -11684,8 +11680,8 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="20" customFormat="1" ht="356.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="163"/>
+    <row r="17" spans="1:10" s="20" customFormat="1" ht="378" x14ac:dyDescent="0.25">
+      <c r="A17" s="174"/>
       <c r="B17" s="37" t="s">
         <v>167</v>
       </c>
@@ -11712,8 +11708,8 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="20" customFormat="1" ht="356.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="163"/>
+    <row r="18" spans="1:10" s="20" customFormat="1" ht="393.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="174"/>
       <c r="B18" s="37" t="s">
         <v>170</v>
       </c>
@@ -11740,8 +11736,8 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="20" customFormat="1" ht="341" x14ac:dyDescent="0.35">
-      <c r="A19" s="163"/>
+    <row r="19" spans="1:10" s="20" customFormat="1" ht="346.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="174"/>
       <c r="B19" s="37" t="s">
         <v>173</v>
       </c>
@@ -11768,8 +11764,8 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="20" customFormat="1" ht="372" x14ac:dyDescent="0.35">
-      <c r="A20" s="163"/>
+    <row r="20" spans="1:10" s="20" customFormat="1" ht="393.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="174"/>
       <c r="B20" s="37" t="s">
         <v>176</v>
       </c>
@@ -11796,8 +11792,8 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="20" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="163" t="s">
+    <row r="21" spans="1:10" s="20" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="174" t="s">
         <v>179</v>
       </c>
       <c r="B21" s="37" t="s">
@@ -11826,8 +11822,8 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="20" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="163"/>
+    <row r="22" spans="1:10" s="20" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="174"/>
       <c r="B22" s="37" t="s">
         <v>183</v>
       </c>
@@ -11854,8 +11850,8 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="20" customFormat="1" ht="356.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="163"/>
+    <row r="23" spans="1:10" s="20" customFormat="1" ht="362.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="174"/>
       <c r="B23" s="37" t="s">
         <v>186</v>
       </c>
@@ -11882,8 +11878,8 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="20" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="163" t="s">
+    <row r="24" spans="1:10" s="20" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="174" t="s">
         <v>1153</v>
       </c>
       <c r="B24" s="37" t="s">
@@ -11901,7 +11897,7 @@
       <c r="F24" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="G24" s="169" t="s">
+      <c r="G24" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H24" s="24" t="s">
@@ -11914,8 +11910,8 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="20" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="163"/>
+    <row r="25" spans="1:10" s="20" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="174"/>
       <c r="B25" s="37" t="s">
         <v>191</v>
       </c>
@@ -11931,7 +11927,7 @@
       <c r="F25" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="G25" s="169" t="s">
+      <c r="G25" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H25" s="24" t="s">
@@ -11944,8 +11940,8 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="20" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="163"/>
+    <row r="26" spans="1:10" s="20" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="174"/>
       <c r="B26" s="37" t="s">
         <v>193</v>
       </c>
@@ -11961,7 +11957,7 @@
       <c r="F26" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="G26" s="169" t="s">
+      <c r="G26" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H26" s="24" t="s">
@@ -11974,8 +11970,8 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="20" customFormat="1" ht="310" x14ac:dyDescent="0.35">
-      <c r="A27" s="163"/>
+    <row r="27" spans="1:10" s="20" customFormat="1" ht="330.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="174"/>
       <c r="B27" s="37" t="s">
         <v>195</v>
       </c>
@@ -11991,7 +11987,7 @@
       <c r="F27" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="G27" s="169" t="s">
+      <c r="G27" s="165" t="s">
         <v>60</v>
       </c>
       <c r="H27" s="24" t="s">
@@ -12004,8 +12000,8 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="20" customFormat="1" ht="341" x14ac:dyDescent="0.35">
-      <c r="A28" s="163"/>
+    <row r="28" spans="1:10" s="20" customFormat="1" ht="362.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="174"/>
       <c r="B28" s="37" t="s">
         <v>197</v>
       </c>
@@ -12021,7 +12017,7 @@
       <c r="F28" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="G28" s="169" t="s">
+      <c r="G28" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H28" s="22"/>
@@ -12032,8 +12028,8 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="20" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="163" t="s">
+    <row r="29" spans="1:10" s="20" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="174" t="s">
         <v>1154</v>
       </c>
       <c r="B29" s="37" t="s">
@@ -12062,8 +12058,8 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="20" customFormat="1" ht="310" x14ac:dyDescent="0.35">
-      <c r="A30" s="163"/>
+    <row r="30" spans="1:10" s="20" customFormat="1" ht="315" x14ac:dyDescent="0.25">
+      <c r="A30" s="174"/>
       <c r="B30" s="37" t="s">
         <v>201</v>
       </c>
@@ -12079,7 +12075,7 @@
       <c r="F30" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="G30" s="169" t="s">
+      <c r="G30" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H30" s="22" t="s">
@@ -12092,8 +12088,8 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="31" spans="1:10" s="20" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="163"/>
+    <row r="31" spans="1:10" s="20" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="174"/>
       <c r="B31" s="37" t="s">
         <v>203</v>
       </c>
@@ -12109,7 +12105,7 @@
       <c r="F31" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="G31" s="169" t="s">
+      <c r="G31" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H31" s="24" t="s">
@@ -12122,8 +12118,8 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="32" spans="1:10" s="20" customFormat="1" ht="310" x14ac:dyDescent="0.35">
-      <c r="A32" s="163"/>
+    <row r="32" spans="1:10" s="20" customFormat="1" ht="330.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="174"/>
       <c r="B32" s="37" t="s">
         <v>205</v>
       </c>
@@ -12139,7 +12135,7 @@
       <c r="F32" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="G32" s="169" t="s">
+      <c r="G32" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H32" s="22" t="s">
@@ -12152,8 +12148,8 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="20" customFormat="1" ht="341" x14ac:dyDescent="0.35">
-      <c r="A33" s="163"/>
+    <row r="33" spans="1:10" s="20" customFormat="1" ht="378" x14ac:dyDescent="0.25">
+      <c r="A33" s="174"/>
       <c r="B33" s="37" t="s">
         <v>207</v>
       </c>
@@ -12169,7 +12165,7 @@
       <c r="F33" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="G33" s="169" t="s">
+      <c r="G33" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H33" s="22" t="s">
@@ -12182,8 +12178,8 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="20" customFormat="1" ht="294.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="163"/>
+    <row r="34" spans="1:10" s="20" customFormat="1" ht="315.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="174"/>
       <c r="B34" s="37" t="s">
         <v>210</v>
       </c>
@@ -12210,8 +12206,8 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="20" customFormat="1" ht="341" x14ac:dyDescent="0.35">
-      <c r="A35" s="163"/>
+    <row r="35" spans="1:10" s="20" customFormat="1" ht="362.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="174"/>
       <c r="B35" s="37" t="s">
         <v>212</v>
       </c>
@@ -12227,7 +12223,7 @@
       <c r="F35" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="G35" s="172" t="s">
+      <c r="G35" s="168" t="s">
         <v>282</v>
       </c>
       <c r="H35" s="22" t="s">
@@ -12240,8 +12236,8 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="20" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="163" t="s">
+    <row r="36" spans="1:10" s="20" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="174" t="s">
         <v>214</v>
       </c>
       <c r="B36" s="37" t="s">
@@ -12259,7 +12255,7 @@
       <c r="F36" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="G36" s="169" t="s">
+      <c r="G36" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H36" s="22" t="s">
@@ -12272,8 +12268,8 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="37" spans="1:10" s="20" customFormat="1" ht="263.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="163"/>
+    <row r="37" spans="1:10" s="20" customFormat="1" ht="284.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="174"/>
       <c r="B37" s="37" t="s">
         <v>218</v>
       </c>
@@ -12290,7 +12286,7 @@
         <v>219</v>
       </c>
       <c r="G37" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H37" s="22"/>
       <c r="I37" s="24" t="s">
@@ -12300,8 +12296,8 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="20" customFormat="1" ht="310" x14ac:dyDescent="0.35">
-      <c r="A38" s="163"/>
+    <row r="38" spans="1:10" s="20" customFormat="1" ht="347.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="174"/>
       <c r="B38" s="37" t="s">
         <v>220</v>
       </c>
@@ -12318,7 +12314,7 @@
         <v>221</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H38" s="22"/>
       <c r="I38" s="24" t="s">
@@ -12328,8 +12324,8 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="20" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="163" t="s">
+    <row r="39" spans="1:10" s="20" customFormat="1" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="174" t="s">
         <v>222</v>
       </c>
       <c r="B39" s="37" t="s">
@@ -12348,7 +12344,7 @@
         <v>225</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H39" s="22"/>
       <c r="I39" s="24" t="s">
@@ -12358,8 +12354,8 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="20" customFormat="1" ht="279" x14ac:dyDescent="0.35">
-      <c r="A40" s="163"/>
+    <row r="40" spans="1:10" s="20" customFormat="1" ht="315.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="174"/>
       <c r="B40" s="37" t="s">
         <v>226</v>
       </c>
@@ -12376,7 +12372,7 @@
         <v>227</v>
       </c>
       <c r="G40" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H40" s="22"/>
       <c r="I40" s="24" t="s">
@@ -12386,8 +12382,8 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="20" customFormat="1" ht="310" x14ac:dyDescent="0.35">
-      <c r="A41" s="163"/>
+    <row r="41" spans="1:10" s="20" customFormat="1" ht="331.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="174"/>
       <c r="B41" s="37" t="s">
         <v>228</v>
       </c>
@@ -12404,7 +12400,7 @@
         <v>229</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H41" s="22"/>
       <c r="I41" s="24" t="s">
@@ -12414,8 +12410,8 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="42" spans="1:10" s="20" customFormat="1" ht="310" x14ac:dyDescent="0.35">
-      <c r="A42" s="163"/>
+    <row r="42" spans="1:10" s="20" customFormat="1" ht="331.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="174"/>
       <c r="B42" s="37" t="s">
         <v>230</v>
       </c>
@@ -12432,7 +12428,7 @@
         <v>231</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H42" s="22"/>
       <c r="I42" s="24" t="s">
@@ -12442,8 +12438,8 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="20" customFormat="1" ht="279" x14ac:dyDescent="0.35">
-      <c r="A43" s="163"/>
+    <row r="43" spans="1:10" s="20" customFormat="1" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="174"/>
       <c r="B43" s="37" t="s">
         <v>232</v>
       </c>
@@ -12460,7 +12456,7 @@
         <v>233</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H43" s="22"/>
       <c r="I43" s="24" t="s">
@@ -12470,8 +12466,8 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="20" customFormat="1" ht="294.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="163"/>
+    <row r="44" spans="1:10" s="20" customFormat="1" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="174"/>
       <c r="B44" s="37" t="s">
         <v>234</v>
       </c>
@@ -12488,7 +12484,7 @@
         <v>235</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H44" s="22"/>
       <c r="I44" s="24" t="s">
@@ -12498,8 +12494,8 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="20" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="163" t="s">
+    <row r="45" spans="1:10" s="20" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="174" t="s">
         <v>236</v>
       </c>
       <c r="B45" s="37" t="s">
@@ -12518,7 +12514,7 @@
         <v>239</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H45" s="22"/>
       <c r="I45" s="24" t="s">
@@ -12528,8 +12524,8 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="20" customFormat="1" ht="279" x14ac:dyDescent="0.35">
-      <c r="A46" s="163"/>
+    <row r="46" spans="1:10" s="20" customFormat="1" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="174"/>
       <c r="B46" s="37" t="s">
         <v>240</v>
       </c>
@@ -12546,7 +12542,7 @@
         <v>241</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H46" s="22"/>
       <c r="I46" s="24" t="s">
@@ -12556,8 +12552,8 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="47" spans="1:10" s="20" customFormat="1" ht="310" x14ac:dyDescent="0.35">
-      <c r="A47" s="163"/>
+    <row r="47" spans="1:10" s="20" customFormat="1" ht="347.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="174"/>
       <c r="B47" s="37" t="s">
         <v>242</v>
       </c>
@@ -12574,7 +12570,7 @@
         <v>243</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H47" s="22"/>
       <c r="I47" s="24" t="s">
@@ -12584,8 +12580,8 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="20" customFormat="1" ht="263.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="163"/>
+    <row r="48" spans="1:10" s="20" customFormat="1" ht="284.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="174"/>
       <c r="B48" s="37" t="s">
         <v>244</v>
       </c>
@@ -12602,7 +12598,7 @@
         <v>245</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H48" s="22"/>
       <c r="I48" s="24" t="s">
@@ -12612,8 +12608,8 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="20" customFormat="1" ht="294.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="163"/>
+    <row r="49" spans="1:10" s="20" customFormat="1" ht="315.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="174"/>
       <c r="B49" s="37" t="s">
         <v>246</v>
       </c>
@@ -12630,7 +12626,7 @@
         <v>248</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H49" s="22"/>
       <c r="I49" s="24" t="s">
@@ -12640,8 +12636,8 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="50" spans="1:10" s="20" customFormat="1" ht="263.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="163"/>
+    <row r="50" spans="1:10" s="20" customFormat="1" ht="284.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="174"/>
       <c r="B50" s="37" t="s">
         <v>249</v>
       </c>
@@ -12658,7 +12654,7 @@
         <v>251</v>
       </c>
       <c r="G50" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H50" s="22"/>
       <c r="I50" s="24" t="s">
@@ -12668,8 +12664,8 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="51" spans="1:10" s="20" customFormat="1" ht="310" x14ac:dyDescent="0.35">
-      <c r="A51" s="163"/>
+    <row r="51" spans="1:10" s="20" customFormat="1" ht="331.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="174"/>
       <c r="B51" s="37" t="s">
         <v>252</v>
       </c>
@@ -12686,7 +12682,7 @@
         <v>254</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H51" s="22"/>
       <c r="I51" s="24" t="s">
@@ -12696,8 +12692,8 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="20" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="163" t="s">
+    <row r="52" spans="1:10" s="20" customFormat="1" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="174" t="s">
         <v>255</v>
       </c>
       <c r="B52" s="37" t="s">
@@ -12716,7 +12712,7 @@
         <v>258</v>
       </c>
       <c r="G52" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H52" s="22"/>
       <c r="I52" s="24" t="s">
@@ -12726,8 +12722,8 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="53" spans="1:10" s="20" customFormat="1" ht="294.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="163"/>
+    <row r="53" spans="1:10" s="20" customFormat="1" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="174"/>
       <c r="B53" s="37" t="s">
         <v>259</v>
       </c>
@@ -12744,7 +12740,7 @@
         <v>260</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H53" s="22"/>
       <c r="I53" s="24" t="s">
@@ -12754,8 +12750,8 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="20" customFormat="1" ht="341" x14ac:dyDescent="0.35">
-      <c r="A54" s="163"/>
+    <row r="54" spans="1:10" s="20" customFormat="1" ht="363" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="174"/>
       <c r="B54" s="37" t="s">
         <v>261</v>
       </c>
@@ -12772,7 +12768,7 @@
         <v>262</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H54" s="22"/>
       <c r="I54" s="24" t="s">
@@ -12782,8 +12778,8 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="20" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="163" t="s">
+    <row r="55" spans="1:10" s="20" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="174" t="s">
         <v>263</v>
       </c>
       <c r="B55" s="37" t="s">
@@ -12802,7 +12798,7 @@
         <v>267</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H55" s="22"/>
       <c r="I55" s="24" t="s">
@@ -12812,8 +12808,8 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="56" spans="1:10" s="20" customFormat="1" ht="279" x14ac:dyDescent="0.35">
-      <c r="A56" s="163"/>
+    <row r="56" spans="1:10" s="20" customFormat="1" ht="299.25" x14ac:dyDescent="0.25">
+      <c r="A56" s="174"/>
       <c r="B56" s="37" t="s">
         <v>268</v>
       </c>
@@ -12830,7 +12826,7 @@
         <v>269</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H56" s="22"/>
       <c r="I56" s="24" t="s">
@@ -12840,8 +12836,8 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="57" spans="1:10" s="20" customFormat="1" ht="294.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="163"/>
+    <row r="57" spans="1:10" s="20" customFormat="1" ht="315" x14ac:dyDescent="0.25">
+      <c r="A57" s="174"/>
       <c r="B57" s="37" t="s">
         <v>270</v>
       </c>
@@ -12858,7 +12854,7 @@
         <v>271</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H57" s="22"/>
       <c r="I57" s="24" t="s">
@@ -12868,8 +12864,8 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="20" customFormat="1" ht="310" x14ac:dyDescent="0.35">
-      <c r="A58" s="163"/>
+    <row r="58" spans="1:10" s="20" customFormat="1" ht="346.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="174"/>
       <c r="B58" s="37" t="s">
         <v>272</v>
       </c>
@@ -12884,7 +12880,7 @@
         <v>273</v>
       </c>
       <c r="G58" s="28" t="s">
-        <v>30</v>
+        <v>282</v>
       </c>
       <c r="H58" s="28"/>
       <c r="I58" s="79" t="s">
@@ -12896,16 +12892,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A39:A44"/>
+    <mergeCell ref="A45:A51"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="A55:A58"/>
     <mergeCell ref="A2:A13"/>
     <mergeCell ref="A14:A20"/>
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="A24:A28"/>
     <mergeCell ref="A29:A35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A39:A44"/>
-    <mergeCell ref="A45:A51"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="A55:A58"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" showErrorMessage="1" sqref="G2:G58" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -12925,21 +12921,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AMJ24"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.81640625" style="51" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="52" customWidth="1"/>
-    <col min="4" max="5" width="8.81640625" style="52"/>
+    <col min="1" max="1" width="40.85546875" style="51" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="20" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" style="52" customWidth="1"/>
+    <col min="4" max="5" width="8.85546875" style="52"/>
     <col min="6" max="6" width="70" style="20" customWidth="1"/>
-    <col min="7" max="7" width="20.54296875" style="20" customWidth="1"/>
-    <col min="8" max="8" width="36.1796875" style="20" customWidth="1"/>
-    <col min="9" max="9" width="35.7265625" style="20" customWidth="1"/>
-    <col min="10" max="10" width="42.81640625" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="7" max="7" width="20.5703125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="36.140625" style="20" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" style="20" customWidth="1"/>
+    <col min="10" max="10" width="42.85546875" style="20" customWidth="1"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.2">
       <c r="A1" s="53" t="s">
         <v>24</v>
       </c>
@@ -12971,7 +12967,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>274</v>
       </c>
@@ -13001,8 +12997,8 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="163" t="s">
+    <row r="3" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="174" t="s">
         <v>277</v>
       </c>
       <c r="B3" s="55" t="s">
@@ -13033,8 +13029,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="163"/>
+    <row r="4" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="174"/>
       <c r="B4" s="55" t="s">
         <v>280</v>
       </c>
@@ -13063,8 +13059,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="93" x14ac:dyDescent="0.35">
-      <c r="A5" s="163"/>
+    <row r="5" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="174"/>
       <c r="B5" s="55" t="s">
         <v>283</v>
       </c>
@@ -13093,8 +13089,8 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="163"/>
+    <row r="6" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="174"/>
       <c r="B6" s="55" t="s">
         <v>285</v>
       </c>
@@ -13123,8 +13119,8 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="163" t="s">
+    <row r="7" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="174" t="s">
         <v>287</v>
       </c>
       <c r="B7" s="55" t="s">
@@ -13142,7 +13138,7 @@
       <c r="F7" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="G7" s="169" t="s">
+      <c r="G7" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -13155,8 +13151,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="163"/>
+    <row r="8" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="174"/>
       <c r="B8" s="55" t="s">
         <v>290</v>
       </c>
@@ -13185,8 +13181,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="124" x14ac:dyDescent="0.35">
-      <c r="A9" s="163"/>
+    <row r="9" spans="1:10" ht="126" x14ac:dyDescent="0.25">
+      <c r="A9" s="174"/>
       <c r="B9" s="55" t="s">
         <v>292</v>
       </c>
@@ -13213,8 +13209,8 @@
         <v>296</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="155" x14ac:dyDescent="0.35">
-      <c r="A10" s="163"/>
+    <row r="10" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="174"/>
       <c r="B10" s="55" t="s">
         <v>297</v>
       </c>
@@ -13243,8 +13239,8 @@
         <v>301</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="163" t="s">
+    <row r="11" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="174" t="s">
         <v>302</v>
       </c>
       <c r="B11" s="55" t="s">
@@ -13275,8 +13271,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="31" x14ac:dyDescent="0.35">
-      <c r="A12" s="163"/>
+    <row r="12" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="174"/>
       <c r="B12" s="55" t="s">
         <v>306</v>
       </c>
@@ -13305,8 +13301,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="163"/>
+    <row r="13" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A13" s="174"/>
       <c r="B13" s="55" t="s">
         <v>308</v>
       </c>
@@ -13335,8 +13331,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="217" x14ac:dyDescent="0.35">
-      <c r="A14" s="163"/>
+    <row r="14" spans="1:10" ht="252" x14ac:dyDescent="0.25">
+      <c r="A14" s="174"/>
       <c r="B14" s="55" t="s">
         <v>311</v>
       </c>
@@ -13365,8 +13361,8 @@
         <v>315</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="155" x14ac:dyDescent="0.35">
-      <c r="A15" s="163"/>
+    <row r="15" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="174"/>
       <c r="B15" s="55" t="s">
         <v>316</v>
       </c>
@@ -13395,8 +13391,8 @@
         <v>319</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="163" t="s">
+    <row r="16" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="174" t="s">
         <v>320</v>
       </c>
       <c r="B16" s="55" t="s">
@@ -13427,8 +13423,8 @@
         <v>326</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="163"/>
+    <row r="17" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="174"/>
       <c r="B17" s="55" t="s">
         <v>327</v>
       </c>
@@ -13455,8 +13451,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="155" x14ac:dyDescent="0.35">
-      <c r="A18" s="163"/>
+    <row r="18" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="174"/>
       <c r="B18" s="55" t="s">
         <v>329</v>
       </c>
@@ -13483,8 +13479,8 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="163" t="s">
+    <row r="19" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="174" t="s">
         <v>331</v>
       </c>
       <c r="B19" s="55" t="s">
@@ -13515,8 +13511,8 @@
         <v>337</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="163"/>
+    <row r="20" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="174"/>
       <c r="B20" s="55" t="s">
         <v>338</v>
       </c>
@@ -13545,7 +13541,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>342</v>
       </c>
@@ -13562,7 +13558,7 @@
       <c r="F21" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="G21" s="175" t="s">
+      <c r="G21" s="171" t="s">
         <v>30</v>
       </c>
       <c r="H21" s="79" t="s">
@@ -13575,13 +13571,13 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="51"/>
     </row>
-    <row r="23" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="51"/>
     </row>
-    <row r="24" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="51"/>
     </row>
   </sheetData>
@@ -13610,21 +13606,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AMJ11"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.453125" style="64" customWidth="1"/>
-    <col min="2" max="2" width="12.26953125" style="65" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="52" customWidth="1"/>
-    <col min="4" max="5" width="8.81640625" style="52"/>
-    <col min="6" max="6" width="68.7265625" style="20" customWidth="1"/>
-    <col min="7" max="7" width="18.1796875" style="20" customWidth="1"/>
-    <col min="8" max="8" width="32.7265625" style="20" customWidth="1"/>
-    <col min="9" max="9" width="27.26953125" style="20" customWidth="1"/>
-    <col min="10" max="10" width="42.1796875" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="1" max="1" width="38.42578125" style="64" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="65" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="52" customWidth="1"/>
+    <col min="4" max="5" width="8.85546875" style="52"/>
+    <col min="6" max="6" width="68.7109375" style="20" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="32.7109375" style="20" customWidth="1"/>
+    <col min="9" max="9" width="27.28515625" style="20" customWidth="1"/>
+    <col min="10" max="10" width="42.140625" style="20" customWidth="1"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="68" customFormat="1" ht="37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="68" customFormat="1" ht="37.5" x14ac:dyDescent="0.2">
       <c r="A1" s="33" t="s">
         <v>24</v>
       </c>
@@ -13656,8 +13652,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="163" t="s">
+    <row r="2" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="174" t="s">
         <v>345</v>
       </c>
       <c r="B2" s="69" t="s">
@@ -13686,8 +13682,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="217" x14ac:dyDescent="0.35">
-      <c r="A3" s="163"/>
+    <row r="3" spans="1:10" ht="267.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="174"/>
       <c r="B3" s="69" t="s">
         <v>348</v>
       </c>
@@ -13714,8 +13710,8 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="163"/>
+    <row r="4" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="174"/>
       <c r="B4" s="69" t="s">
         <v>350</v>
       </c>
@@ -13742,8 +13738,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="163"/>
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="174"/>
       <c r="B5" s="69" t="s">
         <v>352</v>
       </c>
@@ -13764,8 +13760,8 @@
       <c r="I5" s="22"/>
       <c r="J5" s="26"/>
     </row>
-    <row r="6" spans="1:10" ht="263.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="163"/>
+    <row r="6" spans="1:10" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="174"/>
       <c r="B6" s="69" t="s">
         <v>353</v>
       </c>
@@ -13792,8 +13788,8 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="163" t="s">
+    <row r="7" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="174" t="s">
         <v>355</v>
       </c>
       <c r="B7" s="69" t="s">
@@ -13822,8 +13818,8 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="163"/>
+    <row r="8" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="174"/>
       <c r="B8" s="69" t="s">
         <v>358</v>
       </c>
@@ -13837,7 +13833,7 @@
       <c r="F8" s="23" t="s">
         <v>359</v>
       </c>
-      <c r="G8" s="169" t="s">
+      <c r="G8" s="165" t="s">
         <v>30</v>
       </c>
       <c r="H8" s="24" t="s">
@@ -13850,8 +13846,8 @@
         <v>360</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="163" t="s">
+    <row r="9" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="174" t="s">
         <v>361</v>
       </c>
       <c r="B9" s="69" t="s">
@@ -13867,7 +13863,7 @@
       <c r="F9" s="23" t="s">
         <v>363</v>
       </c>
-      <c r="G9" s="172" t="s">
+      <c r="G9" s="168" t="s">
         <v>282</v>
       </c>
       <c r="H9" s="24" t="s">
@@ -13880,8 +13876,8 @@
         <v>364</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="62" x14ac:dyDescent="0.35">
-      <c r="A10" s="163"/>
+    <row r="10" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="174"/>
       <c r="B10" s="69" t="s">
         <v>365</v>
       </c>
@@ -13908,8 +13904,8 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="294.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="163"/>
+    <row r="11" spans="1:10" ht="362.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="174"/>
       <c r="B11" s="69" t="s">
         <v>367</v>
       </c>
@@ -13960,20 +13956,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AMJ31"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="53.453125" style="64" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" style="20" customWidth="1"/>
-    <col min="3" max="5" width="8.81640625" style="52"/>
-    <col min="6" max="6" width="60.7265625" style="20" customWidth="1"/>
-    <col min="7" max="7" width="22.7265625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="41.26953125" style="20" customWidth="1"/>
-    <col min="9" max="9" width="35.26953125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="53.42578125" style="64" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="20" customWidth="1"/>
+    <col min="3" max="5" width="8.85546875" style="52"/>
+    <col min="6" max="6" width="60.7109375" style="20" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" style="20" customWidth="1"/>
+    <col min="8" max="8" width="41.28515625" style="20" customWidth="1"/>
+    <col min="9" max="9" width="35.28515625" style="20" customWidth="1"/>
     <col min="10" max="10" width="29" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.2">
       <c r="A1" s="33" t="s">
         <v>24</v>
       </c>
@@ -14005,8 +14001,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="163" t="s">
+    <row r="2" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="174" t="s">
         <v>369</v>
       </c>
       <c r="B2" s="55" t="s">
@@ -14035,8 +14031,8 @@
         <v>374</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="124" x14ac:dyDescent="0.35">
-      <c r="A3" s="163"/>
+    <row r="3" spans="1:10" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="174"/>
       <c r="B3" s="55" t="s">
         <v>375</v>
       </c>
@@ -14063,8 +14059,8 @@
         <v>379</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="163"/>
+    <row r="4" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="174"/>
       <c r="B4" s="55" t="s">
         <v>380</v>
       </c>
@@ -14091,8 +14087,8 @@
         <v>384</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="186" x14ac:dyDescent="0.35">
-      <c r="A5" s="163"/>
+    <row r="5" spans="1:10" ht="220.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="174"/>
       <c r="B5" s="55" t="s">
         <v>385</v>
       </c>
@@ -14119,8 +14115,8 @@
         <v>389</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="124" x14ac:dyDescent="0.35">
-      <c r="A6" s="163"/>
+    <row r="6" spans="1:10" ht="126" x14ac:dyDescent="0.25">
+      <c r="A6" s="174"/>
       <c r="B6" s="55" t="s">
         <v>390</v>
       </c>
@@ -14147,8 +14143,8 @@
         <v>394</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="163" t="s">
+    <row r="7" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="174" t="s">
         <v>395</v>
       </c>
       <c r="B7" s="55" t="s">
@@ -14175,8 +14171,8 @@
       </c>
       <c r="J7" s="26"/>
     </row>
-    <row r="8" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="163"/>
+    <row r="8" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="174"/>
       <c r="B8" s="55" t="s">
         <v>399</v>
       </c>
@@ -14203,8 +14199,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="62" x14ac:dyDescent="0.35">
-      <c r="A9" s="163"/>
+    <row r="9" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A9" s="174"/>
       <c r="B9" s="55" t="s">
         <v>253</v>
       </c>
@@ -14231,8 +14227,8 @@
         <v>407</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="62" x14ac:dyDescent="0.35">
-      <c r="A10" s="163"/>
+    <row r="10" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A10" s="174"/>
       <c r="B10" s="55" t="s">
         <v>408</v>
       </c>
@@ -14257,8 +14253,8 @@
       </c>
       <c r="J10" s="26"/>
     </row>
-    <row r="11" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="163"/>
+    <row r="11" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A11" s="174"/>
       <c r="B11" s="55" t="s">
         <v>168</v>
       </c>
@@ -14285,8 +14281,8 @@
         <v>415</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="62" x14ac:dyDescent="0.35">
-      <c r="A12" s="163"/>
+    <row r="12" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A12" s="174"/>
       <c r="B12" s="55" t="s">
         <v>171</v>
       </c>
@@ -14311,8 +14307,8 @@
       </c>
       <c r="J12" s="26"/>
     </row>
-    <row r="13" spans="1:10" ht="62" x14ac:dyDescent="0.35">
-      <c r="A13" s="163"/>
+    <row r="13" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A13" s="174"/>
       <c r="B13" s="55" t="s">
         <v>419</v>
       </c>
@@ -14337,8 +14333,8 @@
       </c>
       <c r="J13" s="26"/>
     </row>
-    <row r="14" spans="1:10" ht="62" x14ac:dyDescent="0.35">
-      <c r="A14" s="163"/>
+    <row r="14" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A14" s="174"/>
       <c r="B14" s="55" t="s">
         <v>174</v>
       </c>
@@ -14363,8 +14359,8 @@
       </c>
       <c r="J14" s="26"/>
     </row>
-    <row r="15" spans="1:10" ht="126.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="163" t="s">
+    <row r="15" spans="1:10" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="174" t="s">
         <v>426</v>
       </c>
       <c r="B15" s="55" t="s">
@@ -14391,8 +14387,8 @@
       </c>
       <c r="J15" s="26"/>
     </row>
-    <row r="16" spans="1:10" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="163"/>
+    <row r="16" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="174"/>
       <c r="B16" s="55" t="s">
         <v>431</v>
       </c>
@@ -14417,8 +14413,8 @@
       </c>
       <c r="J16" s="26"/>
     </row>
-    <row r="17" spans="1:10" ht="62" x14ac:dyDescent="0.35">
-      <c r="A17" s="163"/>
+    <row r="17" spans="1:10" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="174"/>
       <c r="B17" s="55" t="s">
         <v>435</v>
       </c>
@@ -14443,8 +14439,8 @@
       </c>
       <c r="J17" s="26"/>
     </row>
-    <row r="18" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="163"/>
+    <row r="18" spans="1:10" ht="189" x14ac:dyDescent="0.25">
+      <c r="A18" s="174"/>
       <c r="B18" s="55" t="s">
         <v>439</v>
       </c>
@@ -14471,8 +14467,8 @@
         <v>443</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="163"/>
+    <row r="19" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="174"/>
       <c r="B19" s="55" t="s">
         <v>444</v>
       </c>
@@ -14499,8 +14495,8 @@
         <v>443</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="62" x14ac:dyDescent="0.35">
-      <c r="A20" s="163"/>
+    <row r="20" spans="1:10" ht="63" x14ac:dyDescent="0.25">
+      <c r="A20" s="174"/>
       <c r="B20" s="55" t="s">
         <v>448</v>
       </c>
@@ -14525,8 +14521,8 @@
       </c>
       <c r="J20" s="26"/>
     </row>
-    <row r="21" spans="1:10" ht="155" x14ac:dyDescent="0.35">
-      <c r="A21" s="163"/>
+    <row r="21" spans="1:10" ht="189" x14ac:dyDescent="0.25">
+      <c r="A21" s="174"/>
       <c r="B21" s="55" t="s">
         <v>452</v>
       </c>
@@ -14553,8 +14549,8 @@
         <v>456</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="163"/>
+    <row r="22" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="174"/>
       <c r="B22" s="55" t="s">
         <v>457</v>
       </c>
@@ -14581,8 +14577,8 @@
         <v>461</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="201.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="163"/>
+    <row r="23" spans="1:10" ht="220.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="174"/>
       <c r="B23" s="55" t="s">
         <v>462</v>
       </c>
@@ -14607,8 +14603,8 @@
       </c>
       <c r="J23" s="26"/>
     </row>
-    <row r="24" spans="1:10" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="163"/>
+    <row r="24" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="174"/>
       <c r="B24" s="55" t="s">
         <v>466</v>
       </c>
@@ -14633,8 +14629,8 @@
       </c>
       <c r="J24" s="26"/>
     </row>
-    <row r="25" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="163" t="s">
+    <row r="25" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="174" t="s">
         <v>470</v>
       </c>
       <c r="B25" s="55" t="s">
@@ -14661,8 +14657,8 @@
       </c>
       <c r="J25" s="26"/>
     </row>
-    <row r="26" spans="1:10" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="163"/>
+    <row r="26" spans="1:10" ht="189" x14ac:dyDescent="0.25">
+      <c r="A26" s="174"/>
       <c r="B26" s="55" t="s">
         <v>475</v>
       </c>
@@ -14687,8 +14683,8 @@
       </c>
       <c r="J26" s="26"/>
     </row>
-    <row r="27" spans="1:10" ht="31" x14ac:dyDescent="0.35">
-      <c r="A27" s="163"/>
+    <row r="27" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="174"/>
       <c r="B27" s="55" t="s">
         <v>479</v>
       </c>
@@ -14713,8 +14709,8 @@
       </c>
       <c r="J27" s="26"/>
     </row>
-    <row r="28" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="163" t="s">
+    <row r="28" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="174" t="s">
         <v>483</v>
       </c>
       <c r="B28" s="55" t="s">
@@ -14741,8 +14737,8 @@
       </c>
       <c r="J28" s="26"/>
     </row>
-    <row r="29" spans="1:10" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="163"/>
+    <row r="29" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="174"/>
       <c r="B29" s="55" t="s">
         <v>488</v>
       </c>
@@ -14767,8 +14763,8 @@
       </c>
       <c r="J29" s="26"/>
     </row>
-    <row r="30" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="163"/>
+    <row r="30" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="174"/>
       <c r="B30" s="55" t="s">
         <v>492</v>
       </c>
@@ -14793,8 +14789,8 @@
       </c>
       <c r="J30" s="26"/>
     </row>
-    <row r="31" spans="1:10" ht="124" x14ac:dyDescent="0.35">
-      <c r="A31" s="163"/>
+    <row r="31" spans="1:10" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A31" s="174"/>
       <c r="B31" s="55" t="s">
         <v>496</v>
       </c>
@@ -14845,21 +14841,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AMJ17"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.26953125" style="64" customWidth="1"/>
-    <col min="2" max="2" width="6.7265625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="52" customWidth="1"/>
-    <col min="4" max="5" width="8.81640625" style="52"/>
-    <col min="6" max="6" width="97.1796875" style="20" customWidth="1"/>
-    <col min="7" max="7" width="8.54296875" style="20" customWidth="1"/>
-    <col min="8" max="8" width="36.1796875" style="20" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" style="64" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="52" customWidth="1"/>
+    <col min="4" max="5" width="8.85546875" style="52"/>
+    <col min="6" max="6" width="97.140625" style="20" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="36.140625" style="20" customWidth="1"/>
     <col min="9" max="9" width="18" style="20" customWidth="1"/>
-    <col min="10" max="10" width="27.26953125" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="10" max="10" width="27.28515625" style="20" customWidth="1"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="36" customFormat="1" ht="42" x14ac:dyDescent="0.2">
       <c r="A1" s="75" t="s">
         <v>24</v>
       </c>
@@ -14891,8 +14887,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="285.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="163" t="s">
+    <row r="2" spans="1:10" ht="285.60000000000002" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="174" t="s">
         <v>500</v>
       </c>
       <c r="B2" s="37" t="s">
@@ -14919,8 +14915,8 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="31" x14ac:dyDescent="0.35">
-      <c r="A3" s="163"/>
+    <row r="3" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="174"/>
       <c r="B3" s="37" t="s">
         <v>503</v>
       </c>
@@ -14941,8 +14937,8 @@
       <c r="I3" s="24"/>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="163"/>
+    <row r="4" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="174"/>
       <c r="B4" s="37" t="s">
         <v>184</v>
       </c>
@@ -14963,8 +14959,8 @@
       <c r="I4" s="24"/>
       <c r="J4" s="25"/>
     </row>
-    <row r="5" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="163" t="s">
+    <row r="5" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="174" t="s">
         <v>506</v>
       </c>
       <c r="B5" s="37" t="s">
@@ -14980,7 +14976,7 @@
       <c r="F5" s="72" t="s">
         <v>508</v>
       </c>
-      <c r="G5" s="167" t="s">
+      <c r="G5" s="163" t="s">
         <v>30</v>
       </c>
       <c r="H5" s="24" t="s">
@@ -14993,8 +14989,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="163"/>
+    <row r="6" spans="1:10" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="174"/>
       <c r="B6" s="37" t="s">
         <v>509</v>
       </c>
@@ -15021,8 +15017,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="31" x14ac:dyDescent="0.35">
-      <c r="A7" s="163"/>
+    <row r="7" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="174"/>
       <c r="B7" s="37" t="s">
         <v>511</v>
       </c>
@@ -15043,8 +15039,8 @@
       <c r="I7" s="24"/>
       <c r="J7" s="25"/>
     </row>
-    <row r="8" spans="1:10" ht="263.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="163"/>
+    <row r="8" spans="1:10" ht="283.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="174"/>
       <c r="B8" s="37" t="s">
         <v>513</v>
       </c>
@@ -15058,7 +15054,7 @@
       <c r="F8" s="72" t="s">
         <v>514</v>
       </c>
-      <c r="G8" s="167" t="s">
+      <c r="G8" s="163" t="s">
         <v>30</v>
       </c>
       <c r="H8" s="24" t="s">
@@ -15071,8 +15067,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="248" x14ac:dyDescent="0.35">
-      <c r="A9" s="163"/>
+    <row r="9" spans="1:10" ht="267.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="174"/>
       <c r="B9" s="37" t="s">
         <v>515</v>
       </c>
@@ -15099,8 +15095,8 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="163"/>
+    <row r="10" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="174"/>
       <c r="B10" s="37" t="s">
         <v>517</v>
       </c>
@@ -15121,8 +15117,8 @@
       <c r="I10" s="24"/>
       <c r="J10" s="25"/>
     </row>
-    <row r="11" spans="1:10" ht="31" x14ac:dyDescent="0.35">
-      <c r="A11" s="163"/>
+    <row r="11" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="174"/>
       <c r="B11" s="37" t="s">
         <v>519</v>
       </c>
@@ -15143,8 +15139,8 @@
       <c r="I11" s="24"/>
       <c r="J11" s="25"/>
     </row>
-    <row r="12" spans="1:10" ht="31" x14ac:dyDescent="0.35">
-      <c r="A12" s="163"/>
+    <row r="12" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="174"/>
       <c r="B12" s="37" t="s">
         <v>521</v>
       </c>
@@ -15165,8 +15161,8 @@
       <c r="I12" s="24"/>
       <c r="J12" s="25"/>
     </row>
-    <row r="13" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="163" t="s">
+    <row r="13" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="174" t="s">
         <v>523</v>
       </c>
       <c r="B13" s="37" t="s">
@@ -15195,8 +15191,8 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="124" x14ac:dyDescent="0.35">
-      <c r="A14" s="163"/>
+    <row r="14" spans="1:10" ht="126" x14ac:dyDescent="0.25">
+      <c r="A14" s="174"/>
       <c r="B14" s="37" t="s">
         <v>526</v>
       </c>
@@ -15223,8 +15219,8 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="31" x14ac:dyDescent="0.35">
-      <c r="A15" s="163"/>
+    <row r="15" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="174"/>
       <c r="B15" s="37" t="s">
         <v>528</v>
       </c>
@@ -15245,8 +15241,8 @@
       <c r="I15" s="24"/>
       <c r="J15" s="25"/>
     </row>
-    <row r="16" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="163" t="s">
+    <row r="16" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="174" t="s">
         <v>530</v>
       </c>
       <c r="B16" s="37" t="s">
@@ -15262,7 +15258,7 @@
       <c r="F16" s="72" t="s">
         <v>532</v>
       </c>
-      <c r="G16" s="167" t="s">
+      <c r="G16" s="163" t="s">
         <v>30</v>
       </c>
       <c r="H16" s="24" t="s">
@@ -15275,8 +15271,8 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="163"/>
+    <row r="17" spans="1:10" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="174"/>
       <c r="B17" s="37" t="s">
         <v>533</v>
       </c>
@@ -15290,7 +15286,7 @@
       <c r="F17" s="73" t="s">
         <v>534</v>
       </c>
-      <c r="G17" s="176" t="s">
+      <c r="G17" s="172" t="s">
         <v>30</v>
       </c>
       <c r="H17" s="79" t="s">
@@ -15328,21 +15324,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AMJ14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.54296875" style="64" customWidth="1"/>
-    <col min="2" max="2" width="6.7265625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="15.1796875" style="52" customWidth="1"/>
-    <col min="4" max="5" width="8.81640625" style="52"/>
-    <col min="6" max="6" width="80.26953125" style="20" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" style="20" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" style="64" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" style="52" customWidth="1"/>
+    <col min="4" max="5" width="8.85546875" style="52"/>
+    <col min="6" max="6" width="80.28515625" style="20" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" style="20" customWidth="1"/>
     <col min="8" max="8" width="31" style="20" customWidth="1"/>
     <col min="9" max="9" width="24" style="20" customWidth="1"/>
-    <col min="10" max="10" width="35.1796875" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="10" max="10" width="35.140625" style="20" customWidth="1"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="74" customFormat="1" ht="21.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="74" customFormat="1" ht="42.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="112" t="s">
         <v>24</v>
       </c>
@@ -15374,8 +15370,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="357" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="164" t="s">
+    <row r="2" spans="1:10" ht="394.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="175" t="s">
         <v>535</v>
       </c>
       <c r="B2" s="98" t="s">
@@ -15404,8 +15400,8 @@
         <v>539</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="279.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="164"/>
+    <row r="3" spans="1:10" ht="315.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="175"/>
       <c r="B3" s="98" t="s">
         <v>322</v>
       </c>
@@ -15430,8 +15426,8 @@
         <v>542</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="295" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="164"/>
+    <row r="4" spans="1:10" ht="315.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="175"/>
       <c r="B4" s="98" t="s">
         <v>543</v>
       </c>
@@ -15458,8 +15454,8 @@
         <v>547</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="264" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="164"/>
+    <row r="5" spans="1:10" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="175"/>
       <c r="B5" s="98" t="s">
         <v>548</v>
       </c>
@@ -15486,8 +15482,8 @@
         <v>552</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="248.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="164" t="s">
+    <row r="6" spans="1:10" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="175" t="s">
         <v>553</v>
       </c>
       <c r="B6" s="98" t="s">
@@ -15503,7 +15499,7 @@
       <c r="F6" s="104" t="s">
         <v>554</v>
       </c>
-      <c r="G6" s="168" t="s">
+      <c r="G6" s="164" t="s">
         <v>30</v>
       </c>
       <c r="H6" s="88" t="s">
@@ -15516,8 +15512,8 @@
         <v>556</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="279.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="164"/>
+    <row r="7" spans="1:10" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="175"/>
       <c r="B7" s="98" t="s">
         <v>557</v>
       </c>
@@ -15544,8 +15540,8 @@
         <v>561</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="248.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="164" t="s">
+    <row r="8" spans="1:10" ht="300" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="175" t="s">
         <v>562</v>
       </c>
       <c r="B8" s="98" t="s">
@@ -15572,8 +15568,8 @@
         <v>566</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="164"/>
+    <row r="9" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="175"/>
       <c r="B9" s="98" t="s">
         <v>567</v>
       </c>
@@ -15594,8 +15590,8 @@
       <c r="I9" s="88"/>
       <c r="J9" s="87"/>
     </row>
-    <row r="10" spans="1:10" ht="264" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="164"/>
+    <row r="10" spans="1:10" ht="268.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="175"/>
       <c r="B10" s="98" t="s">
         <v>569</v>
       </c>
@@ -15620,8 +15616,8 @@
         <v>572</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="279.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="164"/>
+    <row r="11" spans="1:10" ht="315.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="175"/>
       <c r="B11" s="98" t="s">
         <v>573</v>
       </c>
@@ -15644,8 +15640,8 @@
         <v>576</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="372.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="164" t="s">
+    <row r="12" spans="1:10" ht="394.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="175" t="s">
         <v>577</v>
       </c>
       <c r="B12" s="98" t="s">
@@ -15674,8 +15670,8 @@
         <v>582</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="341.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="164"/>
+    <row r="13" spans="1:10" ht="363" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="175"/>
       <c r="B13" s="98" t="s">
         <v>583</v>
       </c>
@@ -15702,8 +15698,8 @@
         <v>587</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="326" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="164"/>
+    <row r="14" spans="1:10" ht="363" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="175"/>
       <c r="B14" s="98" t="s">
         <v>588</v>
       </c>
@@ -15753,20 +15749,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AMJ14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="21" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.26953125" style="64" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" style="20"/>
-    <col min="3" max="5" width="8.81640625" style="52"/>
-    <col min="6" max="6" width="88.81640625" style="20" customWidth="1"/>
-    <col min="7" max="7" width="8.81640625" style="20"/>
-    <col min="8" max="8" width="28.26953125" style="20" customWidth="1"/>
-    <col min="9" max="9" width="26.26953125" style="20" customWidth="1"/>
-    <col min="10" max="10" width="37.7265625" style="20" customWidth="1"/>
-    <col min="11" max="1024" width="8.81640625" style="20"/>
+    <col min="1" max="1" width="37.28515625" style="64" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="20"/>
+    <col min="3" max="5" width="8.85546875" style="52"/>
+    <col min="6" max="6" width="88.85546875" style="20" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="20"/>
+    <col min="8" max="8" width="28.28515625" style="20" customWidth="1"/>
+    <col min="9" max="9" width="26.28515625" style="20" customWidth="1"/>
+    <col min="10" max="10" width="37.7109375" style="20" customWidth="1"/>
+    <col min="11" max="1024" width="8.85546875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1024" s="36" customFormat="1" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1024" s="36" customFormat="1" ht="42.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="75" t="s">
         <v>24</v>
       </c>
@@ -15798,8 +15794,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:1024" ht="409.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="163" t="s">
+    <row r="2" spans="1:1024" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="174" t="s">
         <v>666</v>
       </c>
       <c r="B2" s="37" t="s">
@@ -15830,8 +15826,8 @@
       <c r="AMI2"/>
       <c r="AMJ2"/>
     </row>
-    <row r="3" spans="1:1024" ht="310.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="163"/>
+    <row r="3" spans="1:1024" ht="331.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="174"/>
       <c r="B3" s="37" t="s">
         <v>672</v>
       </c>
@@ -15856,8 +15852,8 @@
         <v>675</v>
       </c>
     </row>
-    <row r="4" spans="1:1024" ht="233" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="163"/>
+    <row r="4" spans="1:1024" ht="252.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="174"/>
       <c r="B4" s="37" t="s">
         <v>676</v>
       </c>
@@ -15882,8 +15878,8 @@
         <v>679</v>
       </c>
     </row>
-    <row r="5" spans="1:1024" ht="279.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="163" t="s">
+    <row r="5" spans="1:1024" ht="284.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="174" t="s">
         <v>680</v>
       </c>
       <c r="B5" s="37" t="s">
@@ -15910,8 +15906,8 @@
         <v>684</v>
       </c>
     </row>
-    <row r="6" spans="1:1024" ht="264" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="163"/>
+    <row r="6" spans="1:1024" ht="315.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="174"/>
       <c r="B6" s="37" t="s">
         <v>685</v>
       </c>
@@ -15938,8 +15934,8 @@
         <v>689</v>
       </c>
     </row>
-    <row r="7" spans="1:1024" ht="264" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="163"/>
+    <row r="7" spans="1:1024" ht="268.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="174"/>
       <c r="B7" s="37" t="s">
         <v>690</v>
       </c>
@@ -15966,8 +15962,8 @@
         <v>694</v>
       </c>
     </row>
-    <row r="8" spans="1:1024" ht="202" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="163"/>
+    <row r="8" spans="1:1024" ht="221.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="174"/>
       <c r="B8" s="37" t="s">
         <v>695</v>
       </c>
@@ -15992,8 +15988,8 @@
         <v>698</v>
       </c>
     </row>
-    <row r="9" spans="1:1024" ht="217.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="163"/>
+    <row r="9" spans="1:1024" ht="221.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="174"/>
       <c r="B9" s="37" t="s">
         <v>699</v>
       </c>
@@ -16020,19 +16016,19 @@
         <v>703</v>
       </c>
     </row>
-    <row r="10" spans="1:1024" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:1024" x14ac:dyDescent="0.35">
       <c r="H10" s="93"/>
     </row>
-    <row r="11" spans="1:1024" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:1024" x14ac:dyDescent="0.35">
       <c r="H11" s="93"/>
     </row>
-    <row r="12" spans="1:1024" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:1024" x14ac:dyDescent="0.35">
       <c r="H12" s="93"/>
     </row>
-    <row r="13" spans="1:1024" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:1024" x14ac:dyDescent="0.35">
       <c r="H13" s="93"/>
     </row>
-    <row r="14" spans="1:1024" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:1024" x14ac:dyDescent="0.35">
       <c r="H14" s="93"/>
     </row>
   </sheetData>
